--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -531,7 +531,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Отчётов: 37 (из них заготовок внешних форм: 4), видов отчётов: 7. Строк с ⚠: 5.</t>
+          <t>Отчётов: 38 (из них заготовок внешних форм: 4), видов отчётов: 6. Строк с ⚠: 5.</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Задолженность — свод по портфелю</t>
+          <t>Задолженность по состоянию на дату</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -668,52 +668,52 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по задолженности»; «20gruppa.xls»; «report-temp.xls» (от разработчиков)</t>
+          <t>старая система «Отчет по задолженности»; «20gruppa.xls»; «report-temp.xls» (выгрузка старой системы)</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr"/>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>Набор колонок выбирает пользователь: в образцах варианты из 17 и 9 колонок</t>
+          <t>В старой системе — «Информация по задолженности»</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="n">
+      <c r="A12" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>ФО-02</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>вид «Погашенные за период»</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Кредит</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>образцы практики по областям</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>«ТАЛАС ПОГАШЕННЫЕ.xls»</t>
-        </is>
-      </c>
-      <c r="H12" s="9" t="inlineStr"/>
-      <c r="I12" s="9" t="inlineStr"/>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>ФО-03</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Детальная задолженность по кредиту (по датам пересчёта)</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Расчёты</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶101; ТЗ 18; старая система</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>старая система, распечатка «Детальный расчет»; «1.pdf», «chakanges/*.pdf» (тело)</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr"/>
+      <c r="I12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -721,17 +721,17 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>ФО-03</t>
+          <t>ФО-04</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Детальная задолженность по кредиту (по датам пересчёта)</t>
+          <t>Погашения за период</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Расчёты</t>
+          <t>Платежи</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -741,90 +741,94 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶101; ТЗ 18; старая система</t>
+          <t>оф. ТЗ ¶490–495; Порядок №41 п. 6 пп. 1; старая система</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>старая система, распечатка «Детальный расчет»; «1.pdf», «chakanges/*.pdf» (тело)</t>
+          <t>старая система «Отчет по погашениям»; «Сейсултан.xlsx» (лист «Информация по погашениям»)</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="n">
+      <c r="A14" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>ФО-04</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Погашения за период</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>вид «Собрано за месяц»</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Платежи</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶490–495; Порядок №41 п. 6 пп. 1; старая система</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Отчет по погашениям»; «Сейсултан.xlsx» (лист «Информация по погашениям»)</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr"/>
-      <c r="I14" s="7" t="inlineStr"/>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>ТЗ 14</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr"/>
+      <c r="I14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="n">
+      <c r="A15" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>ФО-04</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>вид «Собрано за месяц»</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>Платежи</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>ТЗ 14</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr"/>
-      <c r="I15" s="9" t="inlineStr"/>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>ФО-05</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Графики погашения</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>График</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶61, ¶102, ¶418, ¶872–874; старая система</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>старая система «Отчет по графикам»</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr"/>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -832,17 +836,17 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>ФО-05</t>
+          <t>ФО-06</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Графики погашения</t>
+          <t>План-прогноз поступлений</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>График</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -852,18 +856,18 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶61, ¶102, ¶418, ¶872–874; старая система</t>
+          <t>оф. ТЗ ¶75, ¶489; Методика №17 пп. 1.1–2.3; старая система</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по графикам»</t>
+          <t>старая система «Отчет по плану»</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr"/>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>Данные для формы обеспечивает разработчик</t>
+          <t>Правила план-прогноза по группам заёмщиков — Методика №17</t>
         </is>
       </c>
     </row>
@@ -873,17 +877,17 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>ФО-06</t>
+          <t>ФО-07</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>План-прогноз поступлений</t>
+          <t>Начисления процентов и штрафов</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Расчёты</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -893,20 +897,16 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶75, ¶489; Методика №17 пп. 1.1–2.3; старая система</t>
+          <t>оф. ТЗ ¶101; ТЗ 18</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по плану»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr"/>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>Правила план-прогноза по группам заёмщиков — Методика №17</t>
-        </is>
-      </c>
+      <c r="I17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -914,17 +914,17 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>ФО-07</t>
+          <t>ФО-08</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Начисления процентов и штрафов</t>
+          <t>Освоение и транши</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Расчёты</t>
+          <t>Транши</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶101; ТЗ 18</t>
+          <t>оф. ТЗ ¶446, ¶648–650, ¶870; Методика №16 п. 11 пп. 1; ТЗ 06</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
@@ -943,7 +943,11 @@
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr"/>
-      <c r="I18" s="7" t="inlineStr"/>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -951,17 +955,17 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>ФО-08</t>
+          <t>ФО-09</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Освоение и транши</t>
+          <t>Условия кредита и их версии</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Транши</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -971,7 +975,7 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶446, ¶648–650, ¶870; Методика №16 п. 11 пп. 1; ТЗ 06</t>
+          <t>оф. ТЗ ¶419–427</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
@@ -980,11 +984,7 @@
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик</t>
-        </is>
-      </c>
+      <c r="I19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -992,17 +992,17 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>ФО-09</t>
+          <t>ФО-10</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Условия кредита и их версии</t>
+          <t>Реструктуризация — заявки и решения</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Реструктуризация</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶419–427</t>
+          <t>оф. ТЗ ¶87, ¶435–438; Порядок №41 п. 18; ТЗ 15</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
@@ -1024,82 +1024,82 @@
       <c r="I20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>ФО-10</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Реструктуризация — заявки и решения</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>вид «Влияние реструктуризации: условия до и после»</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>Реструктуризация</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶87, ¶435–438; Порядок №41 п. 18; ТЗ 15</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr"/>
-      <c r="I21" s="7" t="inlineStr"/>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶87</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr"/>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>Свод по кредитам за период. Расчёт по одному кредиту для письма — бланк ФО-80</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="n">
+      <c r="A22" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>ФО-10</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>вид «Влияние реструктуризации: условия до и после»</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>Реструктуризация</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶87</t>
-        </is>
-      </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H22" s="9" t="inlineStr"/>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>Свод по кредитам за период. Расчёт по одному кредиту для письма — бланк ФО-80</t>
-        </is>
-      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>ФО-11</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Списание задолженности</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Кредит</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶417; Порядок №41 пп. 62–63; Политика №28 п. 4.1.1 пп. 9, 12; старая система</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>старая система «Отчет по списанию»</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>ФО-11</t>
+          <t>ФО-12</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Списание задолженности</t>
+          <t>Перевод долга</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -1127,12 +1127,12 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶417; Порядок №41 пп. 62–63; Политика №28 п. 4.1.1 пп. 9, 12; старая система</t>
+          <t>оф. ТЗ ¶375–377, ¶428–431; старая система</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по списанию»</t>
+          <t>старая система «Отчет по переводу долга»</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr"/>
@@ -1144,17 +1144,17 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>ФО-12</t>
+          <t>ФО-13</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Перевод долга</t>
+          <t>Целевое использование средств</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Целевое использование</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1164,16 +1164,20 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶375–377, ¶428–431; старая система</t>
+          <t>оф. ТЗ ¶444–445, ¶869; Порядок №41 п. 6 пп. 3; Методика №16 пп. 4, 6, 7, 11; ПКМ №554 Типовое положение пп. 78, 80</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по переводу долга»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr"/>
-      <c r="I24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>Бланки Методики №16 — ФО-75…ФО-78</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -1181,17 +1185,17 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>ФО-13</t>
+          <t>ФО-14</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование средств</t>
+          <t>Залоговое обеспечение — предметы</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -1201,20 +1205,16 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶444–445, ¶869; Порядок №41 п. 6 пп. 3; Методика №16 пп. 4, 6, 7, 11; ПКМ №554 Типовое положение пп. 78, 80</t>
+          <t>оф. ТЗ ¶357, ¶361, ¶475, ¶511, ¶671–682; Порядок №41 п. 10; Положение №12 п. 4.1, прил. 2 п. 2.5; ТЗ 12; старая система</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Отчет по залогу»</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr"/>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>Бланки Методики №16 — ФО-75…ФО-78</t>
-        </is>
-      </c>
+      <c r="I25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>ФО-14</t>
+          <t>ФО-15</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Залоговое обеспечение — предметы</t>
+          <t>Акты обследования залога</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -1242,16 +1242,20 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶357, ¶361, ¶475, ¶511, ¶671–682; Порядок №41 п. 10; Положение №12 п. 4.1, прил. 2 п. 2.5; ТЗ 12; старая система</t>
+          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Положение №12 п. 5.3; старая система</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по залогу»</t>
+          <t>старая система «Отчет по актам обследования»</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr"/>
-      <c r="I26" s="7" t="inlineStr"/>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик. Бланк акта — ФО-43</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -1259,12 +1263,12 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>ФО-15</t>
+          <t>ФО-16</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Акты обследования залога</t>
+          <t>Снятие с ареста (запрета на отчуждение)</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -1279,20 +1283,16 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Положение №12 п. 5.3; старая система</t>
+          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по актам обследования»</t>
+          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик. Бланк акта — ФО-43</t>
-        </is>
-      </c>
+      <c r="I27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>ФО-16</t>
+          <t>ФО-17</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Снятие с ареста (запрета на отчуждение)</t>
+          <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -1320,57 +1320,57 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
+          <t>оф. ТЗ ¶93, ¶96, ¶557–593, ¶621–622; Порядок №41 пп. 20, 21, 25, 27–29, 37, 53, 58, 59, 61; ТЗ 13; старая система</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
+          <t>старая система «Отчет по взысканию»</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr"/>
-      <c r="I28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>Отбор по виду документа взыскания, включая документы, которые система только учитывает (оф. ТЗ ¶557–585)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>ФО-17</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>Взыскание</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶93, ¶96, ¶557–593, ¶621–622; Порядок №41 пп. 20, 21, 25, 27–29, 37, 53, 58, 59, 61; ТЗ 13; старая система</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Отчет по взысканию»</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr"/>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>Отбор по виду документа взыскания, включая документы, которые система только учитывает (оф. ТЗ ¶557–585)</t>
-        </is>
-      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶582–583; старая система</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>старая система «Отчет ОИП»</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr"/>
+      <c r="I29" s="9" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="9" t="n">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
+          <t>вид «Претензии по областям за период»</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
@@ -1398,12 +1398,12 @@
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶582–583; старая система</t>
+          <t>оф. ТЗ ¶553–556; образец практики</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>старая система «Отчет ОИП»</t>
+          <t>«Претензии по 7 областям.xls»</t>
         </is>
       </c>
       <c r="H30" s="9" t="inlineStr"/>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>вид «Претензии по областям за период»</t>
+          <t>вид «События фазы по датам и времени»</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
@@ -1435,53 +1435,57 @@
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶553–556; образец практики</t>
+          <t>оф. ТЗ ¶627</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>«Претензии по 7 областям.xls»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr"/>
       <c r="I31" s="9" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="n">
+      <c r="A32" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>ФО-17</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>вид «События фазы по датам и времени»</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>Взыскание</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶627</t>
-        </is>
-      </c>
-      <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H32" s="9" t="inlineStr"/>
-      <c r="I32" s="9" t="inlineStr"/>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>ФО-18</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Оформление — комплектность кредитно-залогового дела</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Оформление</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>старая система «Отчет по оформлению»</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr"/>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -1489,17 +1493,17 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>ФО-18</t>
+          <t>ФО-19</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Оформление — комплектность кредитно-залогового дела</t>
+          <t>Документооборот — входящие и исходящие</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Оформление</t>
+          <t>Документооборот</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -1509,12 +1513,12 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
+          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по оформлению»</t>
+          <t>старая система «Отчет по документообороту»</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr"/>
@@ -1530,17 +1534,17 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>ФО-19</t>
+          <t>ФО-20</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Документооборот — входящие и исходящие</t>
+          <t>Задания и их исполнение</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Документооборот</t>
+          <t>Задания</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -1550,12 +1554,12 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
+          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по документообороту»</t>
+          <t>старая система «Контроль исполнения» (частично)</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr"/>
@@ -1571,17 +1575,17 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>ФО-20</t>
+          <t>ФО-24</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Задания и их исполнение</t>
+          <t>Классификация — движение по группам платёжеспособности</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Задания</t>
+          <t>Классификация</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -1591,20 +1595,16 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
+          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>старая система «Контроль исполнения» (частично)</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr"/>
-      <c r="I35" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик</t>
-        </is>
-      </c>
+      <c r="I35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -1612,17 +1612,17 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>ФО-24</t>
+          <t>ФО-25</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Классификация — движение по группам платёжеспособности</t>
+          <t>Кураторство — нагрузка и закрепление</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Классификация</t>
+          <t>Кураторство</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
+          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
@@ -1644,78 +1644,78 @@
       <c r="I36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>ФО-25</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Кураторство — нагрузка и закрепление</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>вид «Погашенные заёмщики: месяц × куратор»</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>Кураторство</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr"/>
-      <c r="I37" s="7" t="inlineStr"/>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>образцы практики</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>«Result_3.xlsx», «Result_6.xlsx»</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr"/>
+      <c r="I37" s="9" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="n">
+      <c r="A38" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>ФО-25</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>вид «Погашенные заёмщики: месяц × куратор»</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>Кураторство</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>образцы практики</t>
-        </is>
-      </c>
-      <c r="G38" s="9" t="inlineStr">
-        <is>
-          <t>«Result_3.xlsx», «Result_6.xlsx»</t>
-        </is>
-      </c>
-      <c r="H38" s="9" t="inlineStr"/>
-      <c r="I38" s="9" t="inlineStr"/>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>ФО-26</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Портфель — оперативный срез</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Портфель</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr"/>
+      <c r="I38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>ФО-26</t>
+          <t>ФО-27</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Портфель — оперативный срез</t>
+          <t>Средняя просрочка по департаментам</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
+          <t>оф. ТЗ ¶646; ТЗ 24</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>ФО-27</t>
+          <t>ФО-28</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Средняя просрочка по департаментам</t>
+          <t>Доля проблемных кредитов</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶646; ТЗ 24</t>
+          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
@@ -1797,17 +1797,17 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>ФО-28</t>
+          <t>ФО-47</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Доля проблемных кредитов</t>
+          <t>Реестр имущества на дату</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Портфель</t>
+          <t>Имущество</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
+          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
@@ -1834,17 +1834,17 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>ФО-47</t>
+          <t>ФО-53</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Реестр имущества на дату</t>
+          <t>Расчёт в валюте и курсовая разница за период</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Имущество</t>
+          <t>Расчёты</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
+          <t>оф. ТЗ ¶740</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -1871,17 +1871,17 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>ФО-53</t>
+          <t>ФО-54</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Расчёт в валюте и курсовая разница за период</t>
+          <t>План-факт погашений</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Расчёты</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶740</t>
+          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
@@ -1900,7 +1900,11 @@
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr"/>
-      <c r="I43" s="7" t="inlineStr"/>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>Факт погашений против графика и плановых показателей</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -1908,17 +1912,17 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>ФО-54</t>
+          <t>ФО-55</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>План-факт погашений</t>
+          <t>Заявки по программам и статусам</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Заявка и комиссия</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
@@ -1928,7 +1932,7 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
+          <t>ТЗ 02; ТЗ 03</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
@@ -1937,11 +1941,7 @@
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr"/>
-      <c r="I44" s="7" t="inlineStr">
-        <is>
-          <t>Факт погашений против графика и плановых показателей</t>
-        </is>
-      </c>
+      <c r="I44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -1949,17 +1949,17 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>ФО-55</t>
+          <t>ФО-56</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Заявки по программам и статусам</t>
+          <t>План и факт выдачи</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Заявка и комиссия</t>
+          <t>Кредитная программа</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 02; ТЗ 03</t>
+          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
@@ -1978,7 +1978,11 @@
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr"/>
-      <c r="I45" s="7" t="inlineStr"/>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>Плановые показатели выдачи — справочник</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -1986,27 +1990,27 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>ФО-56</t>
+          <t>ФО-57</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>План и факт выдачи</t>
+          <t>Данные для расчёта ОКУ на дату</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Кредитная программа</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>служба рисков</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
+          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
@@ -2017,7 +2021,7 @@
       <c r="H46" s="7" t="inlineStr"/>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>Плановые показатели выдачи — справочник</t>
+          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
         </is>
       </c>
     </row>
@@ -2027,27 +2031,27 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>ФО-57</t>
+          <t>ФО-58</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Данные для расчёта ОКУ на дату</t>
+          <t>Изменения статусов кредитов за период</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>служба рисков</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
+          <t>оф. ТЗ ¶59</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
@@ -2056,11 +2060,7 @@
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr"/>
-      <c r="I47" s="7" t="inlineStr">
-        <is>
-          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
-        </is>
-      </c>
+      <c r="I47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -2068,27 +2068,27 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>ФО-58</t>
+          <t>ФО-59</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Изменения статусов кредитов за период</t>
+          <t>Кредитный риск портфеля</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>Правление</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶59</t>
+          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
@@ -2096,8 +2096,16 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="H48" s="7" t="inlineStr"/>
-      <c r="I48" s="7" t="inlineStr"/>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>Состав показателей — от службы рисков</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>Раз в квартал</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -2105,27 +2113,27 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>ФО-59</t>
+          <t>ФО-91</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Кредитный риск портфеля</t>
+          <t>Отчёт для Министерства финансов (заготовка)</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Внешняя отчётность</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Правление</t>
+          <t>Министерство финансов</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
+          <t>ТЗ 20 п. 13.7</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
@@ -2135,14 +2143,10 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Состав показателей — от службы рисков</t>
-        </is>
-      </c>
-      <c r="I49" s="7" t="inlineStr">
-        <is>
-          <t>Раз в квартал</t>
-        </is>
-      </c>
+          <t>Образец формы. Без образца к заморозке строка снимается</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -2150,12 +2154,12 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>ФО-91</t>
+          <t>ФО-92</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Министерства финансов (заготовка)</t>
+          <t>Отчёт для Кабинета Министров (заготовка)</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
@@ -2165,7 +2169,7 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Министерство финансов</t>
+          <t>Кабинет Министров</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -2191,12 +2195,12 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>ФО-92</t>
+          <t>ФО-93</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Кабинета Министров (заготовка)</t>
+          <t>Отчёт для Национального статистического комитета (заготовка)</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -2206,7 +2210,7 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Кабинет Министров</t>
+          <t>Нацстатком</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -2232,12 +2236,12 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>ФО-93</t>
+          <t>ФО-94</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Национального статистического комитета (заготовка)</t>
+          <t>Отчёт для банка-агента (заготовка)</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -2247,7 +2251,7 @@
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>Нацстатком</t>
+          <t>банк-агент</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -2273,39 +2277,35 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>ФО-94</t>
+          <t>ФО-95</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для банка-агента (заготовка)</t>
+          <t>Погашенные кредиты за период</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Внешняя отчётность</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>банк-агент</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 20 п. 13.7</t>
+          <t>решение владельца 29.10.2026: выделен из вида ФО-02; закрытие кредитно-залоговых дел и снятие обременений после погашения</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H53" s="11" t="inlineStr">
-        <is>
-          <t>Образец формы. Без образца к заморозке строка снимается</t>
-        </is>
-      </c>
+          <t>нет — новая форма</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr"/>
       <c r="I53" s="7" t="inlineStr"/>
     </row>
   </sheetData>

--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Перечень отчётов" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень отчётов'!$A$9:$I$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень отчётов'!$A$9:$I$52</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Перечень отчётов'!$9:$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -531,7 +531,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Отчётов: 38 (из них заготовок внешних форм: 4), видов отчётов: 6. Строк с ⚠: 5.</t>
+          <t>Отчётов: 37 (из них заготовок внешних форм: 4), видов отчётов: 6. Строк с ⚠: 5.</t>
         </is>
       </c>
     </row>
@@ -684,17 +684,17 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>ФО-03</t>
+          <t>ФО-04</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Детальная задолженность по кредиту (по датам пересчёта)</t>
+          <t>Погашения за период</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Расчёты</t>
+          <t>Платежи</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -704,90 +704,94 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶101; ТЗ 18; старая система</t>
+          <t>оф. ТЗ ¶490–495; Порядок №41 п. 6 пп. 1; старая система</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>старая система, распечатка «Детальный расчет»; «1.pdf», «chakanges/*.pdf» (тело)</t>
+          <t>старая система «Отчет по погашениям»; «Сейсултан.xlsx» (лист «Информация по погашениям»)</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr"/>
       <c r="I12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n">
+      <c r="A13" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>ФО-04</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Погашения за период</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>вид «Собрано за месяц»</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>Платежи</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶490–495; Порядок №41 п. 6 пп. 1; старая система</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Отчет по погашениям»; «Сейсултан.xlsx» (лист «Информация по погашениям»)</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr"/>
-      <c r="I13" s="7" t="inlineStr"/>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>ТЗ 14</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr"/>
+      <c r="I13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="n">
+      <c r="A14" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>ФО-04</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>вид «Собрано за месяц»</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>Платежи</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>ТЗ 14</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr"/>
-      <c r="I14" s="9" t="inlineStr"/>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>ФО-05</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Графики погашения</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>График</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶61, ¶102, ¶418, ¶872–874; старая система</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>старая система «Отчет по графикам»</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr"/>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -795,17 +799,17 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>ФО-05</t>
+          <t>ФО-06</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Графики погашения</t>
+          <t>План-прогноз поступлений</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>График</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -815,18 +819,18 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶61, ¶102, ¶418, ¶872–874; старая система</t>
+          <t>оф. ТЗ ¶75, ¶489; Методика №17 пп. 1.1–2.3; старая система</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по графикам»</t>
+          <t>старая система «Отчет по плану»</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr"/>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>Данные для формы обеспечивает разработчик</t>
+          <t>Правила план-прогноза по группам заёмщиков — Методика №17</t>
         </is>
       </c>
     </row>
@@ -836,17 +840,17 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>ФО-06</t>
+          <t>ФО-07</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>План-прогноз поступлений</t>
+          <t>Начисления процентов и штрафов</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Расчёты</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -856,20 +860,16 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶75, ¶489; Методика №17 пп. 1.1–2.3; старая система</t>
+          <t>оф. ТЗ ¶101; ТЗ 18</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по плану»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr"/>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>Правила план-прогноза по группам заёмщиков — Методика №17</t>
-        </is>
-      </c>
+      <c r="I16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -877,17 +877,17 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>ФО-07</t>
+          <t>ФО-08</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Начисления процентов и штрафов</t>
+          <t>Освоение и транши</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Расчёты</t>
+          <t>Транши</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶101; ТЗ 18</t>
+          <t>оф. ТЗ ¶446, ¶648–650, ¶870; Методика №16 п. 11 пп. 1; ТЗ 06</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
@@ -906,7 +906,11 @@
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr"/>
-      <c r="I17" s="7" t="inlineStr"/>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -914,17 +918,17 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>ФО-08</t>
+          <t>ФО-09</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Освоение и транши</t>
+          <t>Условия кредита и их версии</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Транши</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -934,7 +938,7 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶446, ¶648–650, ¶870; Методика №16 п. 11 пп. 1; ТЗ 06</t>
+          <t>оф. ТЗ ¶419–427</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
@@ -943,11 +947,7 @@
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr"/>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик</t>
-        </is>
-      </c>
+      <c r="I18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -955,17 +955,17 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>ФО-09</t>
+          <t>ФО-10</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Условия кредита и их версии</t>
+          <t>Реструктуризация — заявки и решения</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Реструктуризация</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶419–427</t>
+          <t>оф. ТЗ ¶87, ¶435–438; Порядок №41 п. 18; ТЗ 15</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
@@ -987,82 +987,82 @@
       <c r="I19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>ФО-10</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>Реструктуризация — заявки и решения</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>вид «Влияние реструктуризации: условия до и после»</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Реструктуризация</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶87, ¶435–438; Порядок №41 п. 18; ТЗ 15</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr"/>
-      <c r="I20" s="7" t="inlineStr"/>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶87</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr"/>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>Свод по кредитам за период. Расчёт по одному кредиту для письма — бланк ФО-80</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="n">
+      <c r="A21" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>ФО-10</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>вид «Влияние реструктуризации: условия до и после»</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>Реструктуризация</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶87</t>
-        </is>
-      </c>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H21" s="9" t="inlineStr"/>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>Свод по кредитам за период. Расчёт по одному кредиту для письма — бланк ФО-80</t>
-        </is>
-      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>ФО-11</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Списание задолженности</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Кредит</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶417; Порядок №41 пп. 62–63; Политика №28 п. 4.1.1 пп. 9, 12; старая система</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>старая система «Отчет по списанию»</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr"/>
+      <c r="I21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>ФО-11</t>
+          <t>ФО-12</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Списание задолженности</t>
+          <t>Перевод долга</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶417; Порядок №41 пп. 62–63; Политика №28 п. 4.1.1 пп. 9, 12; старая система</t>
+          <t>оф. ТЗ ¶375–377, ¶428–431; старая система</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по списанию»</t>
+          <t>старая система «Отчет по переводу долга»</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr"/>
@@ -1107,17 +1107,17 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>ФО-12</t>
+          <t>ФО-13</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Перевод долга</t>
+          <t>Целевое использование средств</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Целевое использование</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -1127,16 +1127,20 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶375–377, ¶428–431; старая система</t>
+          <t>оф. ТЗ ¶444–445, ¶869; Порядок №41 п. 6 пп. 3; Методика №16 пп. 4, 6, 7, 11; ПКМ №554 Типовое положение пп. 78, 80</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по переводу долга»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr"/>
-      <c r="I23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>Бланки Методики №16 — ФО-75…ФО-78</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -1144,17 +1148,17 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>ФО-13</t>
+          <t>ФО-14</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование средств</t>
+          <t>Залоговое обеспечение — предметы</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1164,20 +1168,16 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶444–445, ¶869; Порядок №41 п. 6 пп. 3; Методика №16 пп. 4, 6, 7, 11; ПКМ №554 Типовое положение пп. 78, 80</t>
+          <t>оф. ТЗ ¶357, ¶361, ¶475, ¶511, ¶671–682; Порядок №41 п. 10; Положение №12 п. 4.1, прил. 2 п. 2.5; ТЗ 12; старая система</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Отчет по залогу»</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr"/>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>Бланки Методики №16 — ФО-75…ФО-78</t>
-        </is>
-      </c>
+      <c r="I24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>ФО-14</t>
+          <t>ФО-15</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Залоговое обеспечение — предметы</t>
+          <t>Акты обследования залога</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -1205,16 +1205,20 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶357, ¶361, ¶475, ¶511, ¶671–682; Порядок №41 п. 10; Положение №12 п. 4.1, прил. 2 п. 2.5; ТЗ 12; старая система</t>
+          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Положение №12 п. 5.3; старая система</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по залогу»</t>
+          <t>старая система «Отчет по актам обследования»</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr"/>
-      <c r="I25" s="7" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик. Бланк акта — ФО-43</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -1222,12 +1226,12 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>ФО-15</t>
+          <t>ФО-16</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Акты обследования залога</t>
+          <t>Снятие с ареста (запрета на отчуждение)</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -1242,20 +1246,16 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Положение №12 п. 5.3; старая система</t>
+          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по актам обследования»</t>
+          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr"/>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик. Бланк акта — ФО-43</t>
-        </is>
-      </c>
+      <c r="I26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -1263,17 +1263,17 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>ФО-16</t>
+          <t>ФО-17</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Снятие с ареста (запрета на отчуждение)</t>
+          <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -1283,57 +1283,57 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
+          <t>оф. ТЗ ¶93, ¶96, ¶557–593, ¶621–622; Порядок №41 пп. 20, 21, 25, 27–29, 37, 53, 58, 59, 61; ТЗ 13; старая система</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
+          <t>старая система «Отчет по взысканию»</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Отбор по виду документа взыскания, включая документы, которые система только учитывает (оф. ТЗ ¶557–585)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>ФО-17</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>Взыскание</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶93, ¶96, ¶557–593, ¶621–622; Порядок №41 пп. 20, 21, 25, 27–29, 37, 53, 58, 59, 61; ТЗ 13; старая система</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Отчет по взысканию»</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr"/>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>Отбор по виду документа взыскания, включая документы, которые система только учитывает (оф. ТЗ ¶557–585)</t>
-        </is>
-      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶582–583; старая система</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>старая система «Отчет ОИП»</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr"/>
+      <c r="I28" s="9" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="9" t="n">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
+          <t>вид «Претензии по областям за период»</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
@@ -1361,12 +1361,12 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶582–583; старая система</t>
+          <t>оф. ТЗ ¶553–556; образец практики</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>старая система «Отчет ОИП»</t>
+          <t>«Претензии по 7 областям.xls»</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr"/>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>вид «Претензии по областям за период»</t>
+          <t>вид «События фазы по датам и времени»</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
@@ -1398,53 +1398,57 @@
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶553–556; образец практики</t>
+          <t>оф. ТЗ ¶627</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>«Претензии по 7 областям.xls»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H30" s="9" t="inlineStr"/>
       <c r="I30" s="9" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="n">
+      <c r="A31" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>ФО-17</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>вид «События фазы по датам и времени»</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>Взыскание</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶627</t>
-        </is>
-      </c>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H31" s="9" t="inlineStr"/>
-      <c r="I31" s="9" t="inlineStr"/>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>ФО-18</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Оформление — комплектность кредитно-залогового дела</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Оформление</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>старая система «Отчет по оформлению»</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -1452,17 +1456,17 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>ФО-18</t>
+          <t>ФО-19</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Оформление — комплектность кредитно-залогового дела</t>
+          <t>Документооборот — входящие и исходящие</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Оформление</t>
+          <t>Документооборот</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -1472,12 +1476,12 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
+          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по оформлению»</t>
+          <t>старая система «Отчет по документообороту»</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr"/>
@@ -1493,17 +1497,17 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>ФО-19</t>
+          <t>ФО-20</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Документооборот — входящие и исходящие</t>
+          <t>Задания и их исполнение</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Документооборот</t>
+          <t>Задания</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -1513,12 +1517,12 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
+          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по документообороту»</t>
+          <t>старая система «Контроль исполнения» (частично)</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr"/>
@@ -1534,17 +1538,17 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>ФО-20</t>
+          <t>ФО-24</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Задания и их исполнение</t>
+          <t>Классификация — движение по группам платёжеспособности</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Задания</t>
+          <t>Классификация</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -1554,20 +1558,16 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
+          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>старая система «Контроль исполнения» (частично)</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик</t>
-        </is>
-      </c>
+      <c r="I34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -1575,17 +1575,17 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>ФО-24</t>
+          <t>ФО-25</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Классификация — движение по группам платёжеспособности</t>
+          <t>Кураторство — нагрузка и закрепление</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Классификация</t>
+          <t>Кураторство</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
+          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
@@ -1607,78 +1607,78 @@
       <c r="I35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>ФО-25</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>Кураторство — нагрузка и закрепление</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>вид «Погашенные заёмщики: месяц × куратор»</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
         <is>
           <t>Кураторство</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H36" s="7" t="inlineStr"/>
-      <c r="I36" s="7" t="inlineStr"/>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>образцы практики</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>«Result_3.xlsx», «Result_6.xlsx»</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr"/>
+      <c r="I36" s="9" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="n">
+      <c r="A37" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>ФО-25</t>
-        </is>
-      </c>
-      <c r="C37" s="10" t="inlineStr">
-        <is>
-          <t>вид «Погашенные заёмщики: месяц × куратор»</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>Кураторство</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>образцы практики</t>
-        </is>
-      </c>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t>«Result_3.xlsx», «Result_6.xlsx»</t>
-        </is>
-      </c>
-      <c r="H37" s="9" t="inlineStr"/>
-      <c r="I37" s="9" t="inlineStr"/>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>ФО-26</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Портфель — оперативный срез</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Портфель</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr"/>
+      <c r="I37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>ФО-26</t>
+          <t>ФО-27</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Портфель — оперативный срез</t>
+          <t>Средняя просрочка по департаментам</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
+          <t>оф. ТЗ ¶646; ТЗ 24</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>ФО-27</t>
+          <t>ФО-28</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Средняя просрочка по департаментам</t>
+          <t>Доля проблемных кредитов</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶646; ТЗ 24</t>
+          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
@@ -1760,17 +1760,17 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>ФО-28</t>
+          <t>ФО-47</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Доля проблемных кредитов</t>
+          <t>Реестр имущества на дату</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Портфель</t>
+          <t>Имущество</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
+          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
@@ -1797,17 +1797,17 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>ФО-47</t>
+          <t>ФО-53</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Реестр имущества на дату</t>
+          <t>Расчёт в валюте и курсовая разница за период</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Имущество</t>
+          <t>Расчёты</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
+          <t>оф. ТЗ ¶740</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
@@ -1834,17 +1834,17 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>ФО-53</t>
+          <t>ФО-54</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Расчёт в валюте и курсовая разница за период</t>
+          <t>План-факт погашений</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Расчёты</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶740</t>
+          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -1863,7 +1863,11 @@
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr"/>
-      <c r="I42" s="7" t="inlineStr"/>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>Факт погашений против графика и плановых показателей</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -1871,17 +1875,17 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>ФО-54</t>
+          <t>ФО-55</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>План-факт погашений</t>
+          <t>Заявки по программам и статусам</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Заявка и комиссия</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
@@ -1891,7 +1895,7 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
+          <t>ТЗ 02; ТЗ 03</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
@@ -1900,11 +1904,7 @@
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr"/>
-      <c r="I43" s="7" t="inlineStr">
-        <is>
-          <t>Факт погашений против графика и плановых показателей</t>
-        </is>
-      </c>
+      <c r="I43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -1912,17 +1912,17 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>ФО-55</t>
+          <t>ФО-56</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Заявки по программам и статусам</t>
+          <t>План и факт выдачи</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Заявка и комиссия</t>
+          <t>Кредитная программа</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 02; ТЗ 03</t>
+          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
@@ -1941,7 +1941,11 @@
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr"/>
-      <c r="I44" s="7" t="inlineStr"/>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>Плановые показатели выдачи — справочник</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -1949,27 +1953,27 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>ФО-56</t>
+          <t>ФО-57</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>План и факт выдачи</t>
+          <t>Данные для расчёта ОКУ на дату</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Кредитная программа</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>служба рисков</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
+          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
@@ -1980,7 +1984,7 @@
       <c r="H45" s="7" t="inlineStr"/>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>Плановые показатели выдачи — справочник</t>
+          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
         </is>
       </c>
     </row>
@@ -1990,27 +1994,27 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>ФО-57</t>
+          <t>ФО-58</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Данные для расчёта ОКУ на дату</t>
+          <t>Изменения статусов кредитов за период</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>служба рисков</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
+          <t>оф. ТЗ ¶59</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
@@ -2019,11 +2023,7 @@
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr"/>
-      <c r="I46" s="7" t="inlineStr">
-        <is>
-          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
-        </is>
-      </c>
+      <c r="I46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -2031,27 +2031,27 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>ФО-58</t>
+          <t>ФО-59</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Изменения статусов кредитов за период</t>
+          <t>Кредитный риск портфеля</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>Правление</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶59</t>
+          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
@@ -2059,8 +2059,16 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr"/>
-      <c r="I47" s="7" t="inlineStr"/>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>Состав показателей — от службы рисков</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>Раз в квартал</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -2068,27 +2076,27 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>ФО-59</t>
+          <t>ФО-91</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Кредитный риск портфеля</t>
+          <t>Отчёт для Министерства финансов (заготовка)</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Внешняя отчётность</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Правление</t>
+          <t>Министерство финансов</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
+          <t>ТЗ 20 п. 13.7</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
@@ -2098,14 +2106,10 @@
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>Состав показателей — от службы рисков</t>
-        </is>
-      </c>
-      <c r="I48" s="7" t="inlineStr">
-        <is>
-          <t>Раз в квартал</t>
-        </is>
-      </c>
+          <t>Образец формы. Без образца к заморозке строка снимается</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -2113,12 +2117,12 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>ФО-91</t>
+          <t>ФО-92</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Министерства финансов (заготовка)</t>
+          <t>Отчёт для Кабинета Министров (заготовка)</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
@@ -2128,7 +2132,7 @@
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Министерство финансов</t>
+          <t>Кабинет Министров</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -2154,12 +2158,12 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>ФО-92</t>
+          <t>ФО-93</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Кабинета Министров (заготовка)</t>
+          <t>Отчёт для Национального статистического комитета (заготовка)</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
@@ -2169,7 +2173,7 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Кабинет Министров</t>
+          <t>Нацстатком</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -2195,12 +2199,12 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>ФО-93</t>
+          <t>ФО-94</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Национального статистического комитета (заготовка)</t>
+          <t>Отчёт для банка-агента (заготовка)</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -2210,7 +2214,7 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Нацстатком</t>
+          <t>банк-агент</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -2236,80 +2240,39 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>ФО-94</t>
+          <t>ФО-95</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для банка-агента (заготовка)</t>
+          <t>Погашенные кредиты за период</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Внешняя отчётность</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>банк-агент</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 20 п. 13.7</t>
+          <t>решение владельца 29.10.2026: выделен из вида ФО-02; закрытие кредитно-залоговых дел и снятие обременений после погашения</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H52" s="11" t="inlineStr">
-        <is>
-          <t>Образец формы. Без образца к заморозке строка снимается</t>
-        </is>
-      </c>
+          <t>нет — новая форма</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr"/>
       <c r="I52" s="7" t="inlineStr"/>
     </row>
-    <row r="53">
-      <c r="A53" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>ФО-95</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>Погашенные кредиты за период</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>Кредит</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>решение владельца 29.10.2026: выделен из вида ФО-02; закрытие кредитно-залоговых дел и снятие обременений после погашения</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>нет — новая форма</t>
-        </is>
-      </c>
-      <c r="H53" s="7" t="inlineStr"/>
-      <c r="I53" s="7" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A9:I53"/>
+  <autoFilter ref="A9:I52"/>
   <mergeCells count="5">
     <mergeCell ref="A7:I7"/>
     <mergeCell ref="A2:I2"/>

--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -763,7 +763,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Графики погашения</t>
+          <t>Платежи по графику за период</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -789,7 +789,7 @@
       <c r="H14" s="7" t="inlineStr"/>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>Данные для формы обеспечивает разработчик</t>
+          <t>В старой системе — «Информация по графикам» («Отчет по графикам»)</t>
         </is>
       </c>
     </row>

--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -804,7 +804,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>План-прогноз поступлений</t>
+          <t>План погашений на год</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -830,7 +830,7 @@
       <c r="H15" s="7" t="inlineStr"/>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>Правила план-прогноза по группам заёмщиков — Методика №17</t>
+          <t>В старой системе — «Отчет по плану» («Информация по плановым показателям»); прежнее название — «План-прогноз поступлений»</t>
         </is>
       </c>
     </row>

--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -845,7 +845,7 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Начисления процентов и штрафов</t>
+          <t>Проценты и штрафы за период</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -869,7 +869,11 @@
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr"/>
-      <c r="I16" s="7" t="inlineStr"/>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>Новая форма: в старой системе отчёта не было (тип «LOAN_ACCRUE» без формы); прежнее название — «Начисления процентов и штрафов»</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">

--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Перечень отчётов" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень отчётов'!$A$9:$I$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень отчётов'!$A$9:$I$53</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Перечень отчётов'!$9:$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -531,7 +531,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Отчётов: 37 (из них заготовок внешних форм: 4), видов отчётов: 6. Строк с ⚠: 5.</t>
+          <t>Отчётов: 37 (из них заготовок внешних форм: 4), видов отчётов: 7. Строк с ⚠: 5.</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Условия кредита и их версии</t>
+          <t>Условия кредитов по состоянию на дату</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -951,122 +951,126 @@
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr"/>
-      <c r="I18" s="7" t="inlineStr"/>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>Новая форма: в старой системе отчёта не было (условия — во вкладке «Условия кредита» по одному кредиту); прежнее название — «Условия кредита и их версии»</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>ФО-09</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>вид «Изменения условий кредитов за период»</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Кредит</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶419–427; ТЗ 05</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr"/>
+      <c r="I19" s="9" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>ФО-10</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Реструктуризация — заявки и решения</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>Реструктуризация</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>оф. ТЗ ¶87, ¶435–438; Порядок №41 п. 18; ТЗ 15</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr"/>
+      <c r="I20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>ФО-10</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>вид «Влияние реструктуризации: условия до и после»</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>Реструктуризация</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>оф. ТЗ ¶87</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr"/>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr"/>
+      <c r="I21" s="9" t="inlineStr">
         <is>
           <t>Свод по кредитам за период. Расчёт по одному кредиту для письма — бланк ФО-80</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>ФО-11</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Списание задолженности</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Кредит</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶417; Порядок №41 пп. 62–63; Политика №28 п. 4.1.1 пп. 9, 12; старая система</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Отчет по списанию»</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr"/>
-      <c r="I21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -1074,12 +1078,12 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>ФО-12</t>
+          <t>ФО-11</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Перевод долга</t>
+          <t>Списание задолженности</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -1094,12 +1098,12 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶375–377, ¶428–431; старая система</t>
+          <t>оф. ТЗ ¶417; Порядок №41 пп. 62–63; Политика №28 п. 4.1.1 пп. 9, 12; старая система</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по переводу долга»</t>
+          <t>старая система «Отчет по списанию»</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr"/>
@@ -1111,17 +1115,17 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>ФО-13</t>
+          <t>ФО-12</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование средств</t>
+          <t>Перевод долга</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -1131,20 +1135,16 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶444–445, ¶869; Порядок №41 п. 6 пп. 3; Методика №16 пп. 4, 6, 7, 11; ПКМ №554 Типовое положение пп. 78, 80</t>
+          <t>оф. ТЗ ¶375–377, ¶428–431; старая система</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Отчет по переводу долга»</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr"/>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>Бланки Методики №16 — ФО-75…ФО-78</t>
-        </is>
-      </c>
+      <c r="I23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -1152,17 +1152,17 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>ФО-14</t>
+          <t>ФО-13</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Залоговое обеспечение — предметы</t>
+          <t>Целевое использование средств</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Целевое использование</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1172,16 +1172,20 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶357, ¶361, ¶475, ¶511, ¶671–682; Порядок №41 п. 10; Положение №12 п. 4.1, прил. 2 п. 2.5; ТЗ 12; старая система</t>
+          <t>оф. ТЗ ¶444–445, ¶869; Порядок №41 п. 6 пп. 3; Методика №16 пп. 4, 6, 7, 11; ПКМ №554 Типовое положение пп. 78, 80</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по залогу»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr"/>
-      <c r="I24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>Бланки Методики №16 — ФО-75…ФО-78</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -1189,12 +1193,12 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>ФО-15</t>
+          <t>ФО-14</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Акты обследования залога</t>
+          <t>Залоговое обеспечение — предметы</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -1209,20 +1213,16 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Положение №12 п. 5.3; старая система</t>
+          <t>оф. ТЗ ¶357, ¶361, ¶475, ¶511, ¶671–682; Порядок №41 п. 10; Положение №12 п. 4.1, прил. 2 п. 2.5; ТЗ 12; старая система</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по актам обследования»</t>
+          <t>старая система «Отчет по залогу»</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr"/>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик. Бланк акта — ФО-43</t>
-        </is>
-      </c>
+      <c r="I25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>ФО-16</t>
+          <t>ФО-15</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Снятие с ареста (запрета на отчуждение)</t>
+          <t>Акты обследования залога</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -1250,16 +1250,20 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
+          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Положение №12 п. 5.3; старая система</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
+          <t>старая система «Отчет по актам обследования»</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr"/>
-      <c r="I26" s="7" t="inlineStr"/>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик. Бланк акта — ФО-43</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -1267,77 +1271,77 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
+          <t>ФО-16</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Снятие с ареста (запрета на отчуждение)</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Залог</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
           <t>ФО-17</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>Взыскание</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>оф. ТЗ ¶93, ¶96, ¶557–593, ¶621–622; Порядок №41 пп. 20, 21, 25, 27–29, 37, 53, 58, 59, 61; ТЗ 13; старая система</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>старая система «Отчет по взысканию»</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>Отбор по виду документа взыскания, включая документы, которые система только учитывает (оф. ТЗ ¶557–585)</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>ФО-17</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>Взыскание</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶582–583; старая система</t>
-        </is>
-      </c>
-      <c r="G28" s="9" t="inlineStr">
-        <is>
-          <t>старая система «Отчет ОИП»</t>
-        </is>
-      </c>
-      <c r="H28" s="9" t="inlineStr"/>
-      <c r="I28" s="9" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="9" t="n">
@@ -1350,7 +1354,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>вид «Претензии по областям за период»</t>
+          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
@@ -1365,12 +1369,12 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶553–556; образец практики</t>
+          <t>оф. ТЗ ¶582–583; старая система</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>«Претензии по 7 областям.xls»</t>
+          <t>старая система «Отчет ОИП»</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr"/>
@@ -1387,7 +1391,7 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>вид «События фазы по датам и времени»</t>
+          <t>вид «Претензии по областям за период»</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
@@ -1402,57 +1406,53 @@
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶627</t>
+          <t>оф. ТЗ ¶553–556; образец практики</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>«Претензии по 7 областям.xls»</t>
         </is>
       </c>
       <c r="H30" s="9" t="inlineStr"/>
       <c r="I30" s="9" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>ФО-18</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>Оформление — комплектность кредитно-залогового дела</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>Оформление</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Отчет по оформлению»</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr"/>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик</t>
-        </is>
-      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>ФО-17</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>вид «События фазы по датам и времени»</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>Взыскание</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶627</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr"/>
+      <c r="I31" s="9" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>ФО-19</t>
+          <t>ФО-18</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Документооборот — входящие и исходящие</t>
+          <t>Оформление — комплектность кредитно-залогового дела</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Документооборот</t>
+          <t>Оформление</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
+          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по документообороту»</t>
+          <t>старая система «Отчет по оформлению»</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr"/>
@@ -1501,17 +1501,17 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>ФО-20</t>
+          <t>ФО-19</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Задания и их исполнение</t>
+          <t>Документооборот — входящие и исходящие</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Задания</t>
+          <t>Документооборот</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -1521,12 +1521,12 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
+          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>старая система «Контроль исполнения» (частично)</t>
+          <t>старая система «Отчет по документообороту»</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr"/>
@@ -1542,17 +1542,17 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>ФО-24</t>
+          <t>ФО-20</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Классификация — движение по группам платёжеспособности</t>
+          <t>Задания и их исполнение</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Классификация</t>
+          <t>Задания</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -1562,16 +1562,20 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
+          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Контроль исполнения» (частично)</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" s="7" t="inlineStr"/>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -1579,17 +1583,17 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>ФО-25</t>
+          <t>ФО-24</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Кураторство — нагрузка и закрепление</t>
+          <t>Классификация — движение по группам платёжеспособности</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Кураторство</t>
+          <t>Классификация</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -1599,7 +1603,7 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
+          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
@@ -1611,78 +1615,78 @@
       <c r="I35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="n">
+      <c r="A36" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>ФО-25</t>
         </is>
       </c>
-      <c r="C36" s="10" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Кураторство — нагрузка и закрепление</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Кураторство</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr"/>
+      <c r="I36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>ФО-25</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>вид «Погашенные заёмщики: месяц × куратор»</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>Кураторство</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F36" s="9" t="inlineStr">
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
         <is>
           <t>образцы практики</t>
         </is>
       </c>
-      <c r="G36" s="9" t="inlineStr">
+      <c r="G37" s="9" t="inlineStr">
         <is>
           <t>«Result_3.xlsx», «Result_6.xlsx»</t>
         </is>
       </c>
-      <c r="H36" s="9" t="inlineStr"/>
-      <c r="I36" s="9" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>ФО-26</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Портфель — оперативный срез</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>Портфель</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr"/>
-      <c r="I37" s="7" t="inlineStr"/>
+      <c r="H37" s="9" t="inlineStr"/>
+      <c r="I37" s="9" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -1690,12 +1694,12 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>ФО-27</t>
+          <t>ФО-26</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Средняя просрочка по департаментам</t>
+          <t>Портфель — оперативный срез</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
@@ -1710,7 +1714,7 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶646; ТЗ 24</t>
+          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
@@ -1727,12 +1731,12 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>ФО-28</t>
+          <t>ФО-27</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Доля проблемных кредитов</t>
+          <t>Средняя просрочка по департаментам</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
@@ -1747,7 +1751,7 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
+          <t>оф. ТЗ ¶646; ТЗ 24</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
@@ -1764,17 +1768,17 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>ФО-47</t>
+          <t>ФО-28</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Реестр имущества на дату</t>
+          <t>Доля проблемных кредитов</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Имущество</t>
+          <t>Портфель</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
@@ -1784,7 +1788,7 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
+          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
@@ -1801,17 +1805,17 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>ФО-53</t>
+          <t>ФО-47</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Расчёт в валюте и курсовая разница за период</t>
+          <t>Реестр имущества на дату</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Расчёты</t>
+          <t>Имущество</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
@@ -1821,7 +1825,7 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶740</t>
+          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
@@ -1838,17 +1842,17 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>ФО-54</t>
+          <t>ФО-53</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>План-факт погашений</t>
+          <t>Расчёт в валюте и курсовая разница за период</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Расчёты</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
@@ -1858,7 +1862,7 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
+          <t>оф. ТЗ ¶740</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -1867,11 +1871,7 @@
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr"/>
-      <c r="I42" s="7" t="inlineStr">
-        <is>
-          <t>Факт погашений против графика и плановых показателей</t>
-        </is>
-      </c>
+      <c r="I42" s="7" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -1879,17 +1879,17 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>ФО-55</t>
+          <t>ФО-54</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Заявки по программам и статусам</t>
+          <t>План-факт погашений</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Заявка и комиссия</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 02; ТЗ 03</t>
+          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
@@ -1908,7 +1908,11 @@
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr"/>
-      <c r="I43" s="7" t="inlineStr"/>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>Факт погашений против графика и плановых показателей</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -1916,17 +1920,17 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>ФО-56</t>
+          <t>ФО-55</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>План и факт выдачи</t>
+          <t>Заявки по программам и статусам</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Кредитная программа</t>
+          <t>Заявка и комиссия</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
@@ -1936,7 +1940,7 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
+          <t>ТЗ 02; ТЗ 03</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
@@ -1945,11 +1949,7 @@
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr"/>
-      <c r="I44" s="7" t="inlineStr">
-        <is>
-          <t>Плановые показатели выдачи — справочник</t>
-        </is>
-      </c>
+      <c r="I44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -1957,27 +1957,27 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>ФО-57</t>
+          <t>ФО-56</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Данные для расчёта ОКУ на дату</t>
+          <t>План и факт выдачи</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Кредитная программа</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>служба рисков</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
+          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
@@ -1988,7 +1988,7 @@
       <c r="H45" s="7" t="inlineStr"/>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
+          <t>Плановые показатели выдачи — справочник</t>
         </is>
       </c>
     </row>
@@ -1998,27 +1998,27 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>ФО-58</t>
+          <t>ФО-57</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Изменения статусов кредитов за период</t>
+          <t>Данные для расчёта ОКУ на дату</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>служба рисков</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶59</t>
+          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
@@ -2027,7 +2027,11 @@
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr"/>
-      <c r="I46" s="7" t="inlineStr"/>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -2035,27 +2039,27 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>ФО-59</t>
+          <t>ФО-58</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Кредитный риск портфеля</t>
+          <t>Изменения статусов кредитов за период</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>Правление</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
+          <t>оф. ТЗ ¶59</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
@@ -2063,16 +2067,8 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="H47" s="11" t="inlineStr">
-        <is>
-          <t>Состав показателей — от службы рисков</t>
-        </is>
-      </c>
-      <c r="I47" s="7" t="inlineStr">
-        <is>
-          <t>Раз в квартал</t>
-        </is>
-      </c>
+      <c r="H47" s="7" t="inlineStr"/>
+      <c r="I47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -2080,27 +2076,27 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>ФО-91</t>
+          <t>ФО-59</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Министерства финансов (заготовка)</t>
+          <t>Кредитный риск портфеля</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Внешняя отчётность</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Министерство финансов</t>
+          <t>Правление</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 20 п. 13.7</t>
+          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
@@ -2110,10 +2106,14 @@
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>Образец формы. Без образца к заморозке строка снимается</t>
-        </is>
-      </c>
-      <c r="I48" s="7" t="inlineStr"/>
+          <t>Состав показателей — от службы рисков</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>Раз в квартал</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -2121,12 +2121,12 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>ФО-92</t>
+          <t>ФО-91</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Кабинета Министров (заготовка)</t>
+          <t>Отчёт для Министерства финансов (заготовка)</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Кабинет Министров</t>
+          <t>Министерство финансов</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>ФО-93</t>
+          <t>ФО-92</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Национального статистического комитета (заготовка)</t>
+          <t>Отчёт для Кабинета Министров (заготовка)</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Нацстатком</t>
+          <t>Кабинет Министров</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -2203,12 +2203,12 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>ФО-94</t>
+          <t>ФО-93</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для банка-агента (заготовка)</t>
+          <t>Отчёт для Национального статистического комитета (заготовка)</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>банк-агент</t>
+          <t>Нацстатком</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -2244,39 +2244,80 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
+          <t>ФО-94</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>Отчёт для банка-агента (заготовка)</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Внешняя отчётность</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>банк-агент</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>ТЗ 20 п. 13.7</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H52" s="11" t="inlineStr">
+        <is>
+          <t>Образец формы. Без образца к заморозке строка снимается</t>
+        </is>
+      </c>
+      <c r="I52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
           <t>ФО-95</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>Погашенные кредиты за период</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>Кредит</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F52" s="7" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
         <is>
           <t>решение владельца 29.10.2026: выделен из вида ФО-02; закрытие кредитно-залоговых дел и снятие обременений после погашения</t>
         </is>
       </c>
-      <c r="G52" s="7" t="inlineStr">
+      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>нет — новая форма</t>
         </is>
       </c>
-      <c r="H52" s="7" t="inlineStr"/>
-      <c r="I52" s="7" t="inlineStr"/>
+      <c r="H53" s="7" t="inlineStr"/>
+      <c r="I53" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A9:I52"/>
+  <autoFilter ref="A9:I53"/>
   <mergeCells count="5">
     <mergeCell ref="A7:I7"/>
     <mergeCell ref="A2:I2"/>

--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Реструктуризация — заявки и решения</t>
+          <t>Обращения о реструктуризации за период</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -1029,7 +1029,11 @@
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr"/>
-      <c r="I20" s="7" t="inlineStr"/>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>Новая форма: в старой системе реструктуризация велась отдельным кредитом-обёрткой без обращений и стадий; прежнее название — «Реструктуризация — заявки и решения»</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="n">
@@ -1042,7 +1046,7 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>вид «Влияние реструктуризации: условия до и после»</t>
+          <t>вид «Влияние реструктуризации на условия кредитов за период»</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">

--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Перечень отчётов" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень отчётов'!$A$9:$I$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень отчётов'!$A$9:$I$54</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Перечень отчётов'!$9:$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -531,7 +531,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Отчётов: 37 (из них заготовок внешних форм: 4), видов отчётов: 7. Строк с ⚠: 5.</t>
+          <t>Отчётов: 37 (из них заготовок внешних форм: 4), видов отчётов: 8. Строк с ⚠: 5.</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Списание задолженности</t>
+          <t>Списание задолженности за период</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -1111,44 +1111,52 @@
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr"/>
-      <c r="I22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>Прежнее название в старой системе — «Отчет по списанию» («Информация по списанию», по состоянию на дату)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>ФО-12</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>Перевод долга</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>ФО-11</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>вид «Списанная задолженность по состоянию на дату»</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>Кредит</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶375–377, ¶428–431; старая система</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Отчет по переводу долга»</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr"/>
-      <c r="I23" s="7" t="inlineStr"/>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>Порядок №41 пп. 62, 65</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr"/>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>Внебалансовый учёт: списано, поступило после списания, не возвращено, идёт ли взыскание</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -1156,17 +1164,17 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>ФО-13</t>
+          <t>ФО-12</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование средств</t>
+          <t>Перевод долга</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1176,20 +1184,16 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶444–445, ¶869; Порядок №41 п. 6 пп. 3; Методика №16 пп. 4, 6, 7, 11; ПКМ №554 Типовое положение пп. 78, 80</t>
+          <t>оф. ТЗ ¶375–377, ¶428–431; старая система</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Отчет по переводу долга»</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr"/>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>Бланки Методики №16 — ФО-75…ФО-78</t>
-        </is>
-      </c>
+      <c r="I24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -1197,17 +1201,17 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>ФО-14</t>
+          <t>ФО-13</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Залоговое обеспечение — предметы</t>
+          <t>Целевое использование средств</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Целевое использование</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -1217,16 +1221,20 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶357, ¶361, ¶475, ¶511, ¶671–682; Порядок №41 п. 10; Положение №12 п. 4.1, прил. 2 п. 2.5; ТЗ 12; старая система</t>
+          <t>оф. ТЗ ¶444–445, ¶869; Порядок №41 п. 6 пп. 3; Методика №16 пп. 4, 6, 7, 11; ПКМ №554 Типовое положение пп. 78, 80</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по залогу»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr"/>
-      <c r="I25" s="7" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Бланки Методики №16 — ФО-75…ФО-78</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -1234,12 +1242,12 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>ФО-15</t>
+          <t>ФО-14</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Акты обследования залога</t>
+          <t>Залоговое обеспечение — предметы</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -1254,20 +1262,16 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Положение №12 п. 5.3; старая система</t>
+          <t>оф. ТЗ ¶357, ¶361, ¶475, ¶511, ¶671–682; Порядок №41 п. 10; Положение №12 п. 4.1, прил. 2 п. 2.5; ТЗ 12; старая система</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по актам обследования»</t>
+          <t>старая система «Отчет по залогу»</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr"/>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик. Бланк акта — ФО-43</t>
-        </is>
-      </c>
+      <c r="I26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -1275,12 +1279,12 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>ФО-16</t>
+          <t>ФО-15</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Снятие с ареста (запрета на отчуждение)</t>
+          <t>Акты обследования залога</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -1295,16 +1299,20 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
+          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Положение №12 п. 5.3; старая система</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
+          <t>старая система «Отчет по актам обследования»</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик. Бланк акта — ФО-43</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -1312,77 +1320,77 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
+          <t>ФО-16</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Снятие с ареста (запрета на отчуждение)</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Залог</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
           <t>ФО-17</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>Взыскание</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>оф. ТЗ ¶93, ¶96, ¶557–593, ¶621–622; Порядок №41 пп. 20, 21, 25, 27–29, 37, 53, 58, 59, 61; ТЗ 13; старая система</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>старая система «Отчет по взысканию»</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr"/>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>Отбор по виду документа взыскания, включая документы, которые система только учитывает (оф. ТЗ ¶557–585)</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>ФО-17</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>Взыскание</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶582–583; старая система</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t>старая система «Отчет ОИП»</t>
-        </is>
-      </c>
-      <c r="H29" s="9" t="inlineStr"/>
-      <c r="I29" s="9" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="9" t="n">
@@ -1395,7 +1403,7 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>вид «Претензии по областям за период»</t>
+          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
@@ -1410,12 +1418,12 @@
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶553–556; образец практики</t>
+          <t>оф. ТЗ ¶582–583; старая система</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>«Претензии по 7 областям.xls»</t>
+          <t>старая система «Отчет ОИП»</t>
         </is>
       </c>
       <c r="H30" s="9" t="inlineStr"/>
@@ -1432,7 +1440,7 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>вид «События фазы по датам и времени»</t>
+          <t>вид «Претензии по областям за период»</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
@@ -1447,57 +1455,53 @@
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶627</t>
+          <t>оф. ТЗ ¶553–556; образец практики</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>«Претензии по 7 областям.xls»</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr"/>
       <c r="I31" s="9" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>ФО-18</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Оформление — комплектность кредитно-залогового дела</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Оформление</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Отчет по оформлению»</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr"/>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик</t>
-        </is>
-      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>ФО-17</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>вид «События фазы по датам и времени»</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>Взыскание</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶627</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr"/>
+      <c r="I32" s="9" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -1505,17 +1509,17 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>ФО-19</t>
+          <t>ФО-18</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Документооборот — входящие и исходящие</t>
+          <t>Оформление — комплектность кредитно-залогового дела</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Документооборот</t>
+          <t>Оформление</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -1525,12 +1529,12 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
+          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по документообороту»</t>
+          <t>старая система «Отчет по оформлению»</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr"/>
@@ -1546,17 +1550,17 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>ФО-20</t>
+          <t>ФО-19</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Задания и их исполнение</t>
+          <t>Документооборот — входящие и исходящие</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Задания</t>
+          <t>Документооборот</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -1566,12 +1570,12 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
+          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>старая система «Контроль исполнения» (частично)</t>
+          <t>старая система «Отчет по документообороту»</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr"/>
@@ -1587,17 +1591,17 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>ФО-24</t>
+          <t>ФО-20</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Классификация — движение по группам платёжеспособности</t>
+          <t>Задания и их исполнение</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Классификация</t>
+          <t>Задания</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -1607,16 +1611,20 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
+          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Контроль исполнения» (частично)</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr"/>
-      <c r="I35" s="7" t="inlineStr"/>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -1624,17 +1632,17 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>ФО-25</t>
+          <t>ФО-24</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Кураторство — нагрузка и закрепление</t>
+          <t>Классификация — движение по группам платёжеспособности</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Кураторство</t>
+          <t>Классификация</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
@@ -1644,7 +1652,7 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
+          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
@@ -1656,78 +1664,78 @@
       <c r="I36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="n">
+      <c r="A37" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>ФО-25</t>
         </is>
       </c>
-      <c r="C37" s="10" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Кураторство — нагрузка и закрепление</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Кураторство</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr"/>
+      <c r="I37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>ФО-25</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>вид «Погашенные заёмщики: месяц × куратор»</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>Кураторство</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
         <is>
           <t>образцы практики</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr">
+      <c r="G38" s="9" t="inlineStr">
         <is>
           <t>«Result_3.xlsx», «Result_6.xlsx»</t>
         </is>
       </c>
-      <c r="H37" s="9" t="inlineStr"/>
-      <c r="I37" s="9" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>ФО-26</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>Портфель — оперативный срез</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Портфель</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H38" s="7" t="inlineStr"/>
-      <c r="I38" s="7" t="inlineStr"/>
+      <c r="H38" s="9" t="inlineStr"/>
+      <c r="I38" s="9" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -1735,12 +1743,12 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>ФО-27</t>
+          <t>ФО-26</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Средняя просрочка по департаментам</t>
+          <t>Портфель — оперативный срез</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
@@ -1755,7 +1763,7 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶646; ТЗ 24</t>
+          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
@@ -1772,12 +1780,12 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>ФО-28</t>
+          <t>ФО-27</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Доля проблемных кредитов</t>
+          <t>Средняя просрочка по департаментам</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
@@ -1792,7 +1800,7 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
+          <t>оф. ТЗ ¶646; ТЗ 24</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
@@ -1809,17 +1817,17 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>ФО-47</t>
+          <t>ФО-28</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Реестр имущества на дату</t>
+          <t>Доля проблемных кредитов</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Имущество</t>
+          <t>Портфель</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
@@ -1829,7 +1837,7 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
+          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
@@ -1846,17 +1854,17 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>ФО-53</t>
+          <t>ФО-47</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Расчёт в валюте и курсовая разница за период</t>
+          <t>Реестр имущества на дату</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Расчёты</t>
+          <t>Имущество</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
@@ -1866,7 +1874,7 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶740</t>
+          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -1883,17 +1891,17 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>ФО-54</t>
+          <t>ФО-53</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>План-факт погашений</t>
+          <t>Расчёт в валюте и курсовая разница за период</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Расчёты</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
@@ -1903,7 +1911,7 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
+          <t>оф. ТЗ ¶740</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
@@ -1912,11 +1920,7 @@
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr"/>
-      <c r="I43" s="7" t="inlineStr">
-        <is>
-          <t>Факт погашений против графика и плановых показателей</t>
-        </is>
-      </c>
+      <c r="I43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -1924,17 +1928,17 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>ФО-55</t>
+          <t>ФО-54</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Заявки по программам и статусам</t>
+          <t>План-факт погашений</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Заявка и комиссия</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
@@ -1944,7 +1948,7 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 02; ТЗ 03</t>
+          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
@@ -1953,7 +1957,11 @@
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr"/>
-      <c r="I44" s="7" t="inlineStr"/>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>Факт погашений против графика и плановых показателей</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -1961,17 +1969,17 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>ФО-56</t>
+          <t>ФО-55</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>План и факт выдачи</t>
+          <t>Заявки по программам и статусам</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Кредитная программа</t>
+          <t>Заявка и комиссия</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
@@ -1981,7 +1989,7 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
+          <t>ТЗ 02; ТЗ 03</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
@@ -1990,11 +1998,7 @@
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr"/>
-      <c r="I45" s="7" t="inlineStr">
-        <is>
-          <t>Плановые показатели выдачи — справочник</t>
-        </is>
-      </c>
+      <c r="I45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -2002,27 +2006,27 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>ФО-57</t>
+          <t>ФО-56</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Данные для расчёта ОКУ на дату</t>
+          <t>План и факт выдачи</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Кредитная программа</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>служба рисков</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
+          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
@@ -2033,7 +2037,7 @@
       <c r="H46" s="7" t="inlineStr"/>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
+          <t>Плановые показатели выдачи — справочник</t>
         </is>
       </c>
     </row>
@@ -2043,27 +2047,27 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>ФО-58</t>
+          <t>ФО-57</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Изменения статусов кредитов за период</t>
+          <t>Данные для расчёта ОКУ на дату</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>служба рисков</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶59</t>
+          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
@@ -2072,7 +2076,11 @@
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr"/>
-      <c r="I47" s="7" t="inlineStr"/>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -2080,27 +2088,27 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>ФО-59</t>
+          <t>ФО-58</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Кредитный риск портфеля</t>
+          <t>Изменения статусов кредитов за период</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Правление</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
+          <t>оф. ТЗ ¶59</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
@@ -2108,16 +2116,8 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="H48" s="11" t="inlineStr">
-        <is>
-          <t>Состав показателей — от службы рисков</t>
-        </is>
-      </c>
-      <c r="I48" s="7" t="inlineStr">
-        <is>
-          <t>Раз в квартал</t>
-        </is>
-      </c>
+      <c r="H48" s="7" t="inlineStr"/>
+      <c r="I48" s="7" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -2125,27 +2125,27 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>ФО-91</t>
+          <t>ФО-59</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Министерства финансов (заготовка)</t>
+          <t>Кредитный риск портфеля</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Внешняя отчётность</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Министерство финансов</t>
+          <t>Правление</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 20 п. 13.7</t>
+          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
@@ -2155,10 +2155,14 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Образец формы. Без образца к заморозке строка снимается</t>
-        </is>
-      </c>
-      <c r="I49" s="7" t="inlineStr"/>
+          <t>Состав показателей — от службы рисков</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>Раз в квартал</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -2166,12 +2170,12 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>ФО-92</t>
+          <t>ФО-91</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Кабинета Министров (заготовка)</t>
+          <t>Отчёт для Министерства финансов (заготовка)</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
@@ -2181,7 +2185,7 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Кабинет Министров</t>
+          <t>Министерство финансов</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -2207,12 +2211,12 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>ФО-93</t>
+          <t>ФО-92</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Национального статистического комитета (заготовка)</t>
+          <t>Отчёт для Кабинета Министров (заготовка)</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -2222,7 +2226,7 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Нацстатком</t>
+          <t>Кабинет Министров</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -2248,12 +2252,12 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>ФО-94</t>
+          <t>ФО-93</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для банка-агента (заготовка)</t>
+          <t>Отчёт для Национального статистического комитета (заготовка)</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -2263,7 +2267,7 @@
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>банк-агент</t>
+          <t>Нацстатком</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -2289,39 +2293,80 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
+          <t>ФО-94</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>Отчёт для банка-агента (заготовка)</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Внешняя отчётность</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>банк-агент</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>ТЗ 20 п. 13.7</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H53" s="11" t="inlineStr">
+        <is>
+          <t>Образец формы. Без образца к заморозке строка снимается</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
           <t>ФО-95</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>Погашенные кредиты за период</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>Кредит</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
         <is>
           <t>решение владельца 29.10.2026: выделен из вида ФО-02; закрытие кредитно-залоговых дел и снятие обременений после погашения</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr">
+      <c r="G54" s="7" t="inlineStr">
         <is>
           <t>нет — новая форма</t>
         </is>
       </c>
-      <c r="H53" s="7" t="inlineStr"/>
-      <c r="I53" s="7" t="inlineStr"/>
+      <c r="H54" s="7" t="inlineStr"/>
+      <c r="I54" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A9:I53"/>
+  <autoFilter ref="A9:I54"/>
   <mergeCells count="5">
     <mergeCell ref="A7:I7"/>
     <mergeCell ref="A2:I2"/>

--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Перечень отчётов" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень отчётов'!$A$9:$I$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень отчётов'!$A$9:$I$53</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Перечень отчётов'!$9:$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -531,7 +531,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Отчётов: 37 (из них заготовок внешних форм: 4), видов отчётов: 8. Строк с ⚠: 5.</t>
+          <t>Отчётов: 36 (из них заготовок внешних форм: 4), видов отчётов: 8. Строк с ⚠: 5.</t>
         </is>
       </c>
     </row>
@@ -1164,17 +1164,17 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>ФО-12</t>
+          <t>ФО-13</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Перевод долга</t>
+          <t>Целевое использование средств</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Целевое использование</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1184,16 +1184,20 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶375–377, ¶428–431; старая система</t>
+          <t>оф. ТЗ ¶444–445, ¶869; Порядок №41 п. 6 пп. 3; Методика №16 пп. 4, 6, 7, 11; ПКМ №554 Типовое положение пп. 78, 80</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по переводу долга»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr"/>
-      <c r="I24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>Бланки Методики №16 — ФО-75…ФО-78</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -1201,17 +1205,17 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>ФО-13</t>
+          <t>ФО-14</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование средств</t>
+          <t>Залоговое обеспечение — предметы</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -1221,20 +1225,16 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶444–445, ¶869; Порядок №41 п. 6 пп. 3; Методика №16 пп. 4, 6, 7, 11; ПКМ №554 Типовое положение пп. 78, 80</t>
+          <t>оф. ТЗ ¶357, ¶361, ¶475, ¶511, ¶671–682; Порядок №41 п. 10; Положение №12 п. 4.1, прил. 2 п. 2.5; ТЗ 12; старая система</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Отчет по залогу»</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr"/>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>Бланки Методики №16 — ФО-75…ФО-78</t>
-        </is>
-      </c>
+      <c r="I25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>ФО-14</t>
+          <t>ФО-15</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Залоговое обеспечение — предметы</t>
+          <t>Акты обследования залога</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -1262,16 +1262,20 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶357, ¶361, ¶475, ¶511, ¶671–682; Порядок №41 п. 10; Положение №12 п. 4.1, прил. 2 п. 2.5; ТЗ 12; старая система</t>
+          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Положение №12 п. 5.3; старая система</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по залогу»</t>
+          <t>старая система «Отчет по актам обследования»</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr"/>
-      <c r="I26" s="7" t="inlineStr"/>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик. Бланк акта — ФО-43</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -1279,12 +1283,12 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>ФО-15</t>
+          <t>ФО-16</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Акты обследования залога</t>
+          <t>Снятие с ареста (запрета на отчуждение)</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -1299,20 +1303,16 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Положение №12 п. 5.3; старая система</t>
+          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по актам обследования»</t>
+          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик. Бланк акта — ФО-43</t>
-        </is>
-      </c>
+      <c r="I27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -1320,17 +1320,17 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>ФО-16</t>
+          <t>ФО-17</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Снятие с ареста (запрета на отчуждение)</t>
+          <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -1340,57 +1340,57 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
+          <t>оф. ТЗ ¶93, ¶96, ¶557–593, ¶621–622; Порядок №41 пп. 20, 21, 25, 27–29, 37, 53, 58, 59, 61; ТЗ 13; старая система</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
+          <t>старая система «Отчет по взысканию»</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr"/>
-      <c r="I28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>Отбор по виду документа взыскания, включая документы, которые система только учитывает (оф. ТЗ ¶557–585)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>ФО-17</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>Взыскание</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶93, ¶96, ¶557–593, ¶621–622; Порядок №41 пп. 20, 21, 25, 27–29, 37, 53, 58, 59, 61; ТЗ 13; старая система</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Отчет по взысканию»</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr"/>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>Отбор по виду документа взыскания, включая документы, которые система только учитывает (оф. ТЗ ¶557–585)</t>
-        </is>
-      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶582–583; старая система</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>старая система «Отчет ОИП»</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr"/>
+      <c r="I29" s="9" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="9" t="n">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
+          <t>вид «Претензии по областям за период»</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶582–583; старая система</t>
+          <t>оф. ТЗ ¶553–556; образец практики</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>старая система «Отчет ОИП»</t>
+          <t>«Претензии по 7 областям.xls»</t>
         </is>
       </c>
       <c r="H30" s="9" t="inlineStr"/>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>вид «Претензии по областям за период»</t>
+          <t>вид «События фазы по датам и времени»</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
@@ -1455,53 +1455,57 @@
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶553–556; образец практики</t>
+          <t>оф. ТЗ ¶627</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>«Претензии по 7 областям.xls»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr"/>
       <c r="I31" s="9" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="n">
+      <c r="A32" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>ФО-17</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>вид «События фазы по датам и времени»</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>Взыскание</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶627</t>
-        </is>
-      </c>
-      <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H32" s="9" t="inlineStr"/>
-      <c r="I32" s="9" t="inlineStr"/>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>ФО-18</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Оформление — комплектность кредитно-залогового дела</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Оформление</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>старая система «Отчет по оформлению»</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr"/>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -1509,17 +1513,17 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>ФО-18</t>
+          <t>ФО-19</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Оформление — комплектность кредитно-залогового дела</t>
+          <t>Документооборот — входящие и исходящие</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Оформление</t>
+          <t>Документооборот</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -1529,12 +1533,12 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
+          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по оформлению»</t>
+          <t>старая система «Отчет по документообороту»</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr"/>
@@ -1550,17 +1554,17 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>ФО-19</t>
+          <t>ФО-20</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Документооборот — входящие и исходящие</t>
+          <t>Задания и их исполнение</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Документооборот</t>
+          <t>Задания</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -1570,12 +1574,12 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
+          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по документообороту»</t>
+          <t>старая система «Контроль исполнения» (частично)</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr"/>
@@ -1591,17 +1595,17 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>ФО-20</t>
+          <t>ФО-24</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Задания и их исполнение</t>
+          <t>Классификация — движение по группам платёжеспособности</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Задания</t>
+          <t>Классификация</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -1611,20 +1615,16 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
+          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>старая система «Контроль исполнения» (частично)</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr"/>
-      <c r="I35" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик</t>
-        </is>
-      </c>
+      <c r="I35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -1632,17 +1632,17 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>ФО-24</t>
+          <t>ФО-25</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Классификация — движение по группам платёжеспособности</t>
+          <t>Кураторство — нагрузка и закрепление</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Классификация</t>
+          <t>Кураторство</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
+          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
@@ -1664,78 +1664,78 @@
       <c r="I36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>ФО-25</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Кураторство — нагрузка и закрепление</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>вид «Погашенные заёмщики: месяц × куратор»</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>Кураторство</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr"/>
-      <c r="I37" s="7" t="inlineStr"/>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>образцы практики</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>«Result_3.xlsx», «Result_6.xlsx»</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr"/>
+      <c r="I37" s="9" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="n">
+      <c r="A38" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>ФО-25</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>вид «Погашенные заёмщики: месяц × куратор»</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>Кураторство</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>образцы практики</t>
-        </is>
-      </c>
-      <c r="G38" s="9" t="inlineStr">
-        <is>
-          <t>«Result_3.xlsx», «Result_6.xlsx»</t>
-        </is>
-      </c>
-      <c r="H38" s="9" t="inlineStr"/>
-      <c r="I38" s="9" t="inlineStr"/>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>ФО-26</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Портфель — оперативный срез</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Портфель</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr"/>
+      <c r="I38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>ФО-26</t>
+          <t>ФО-27</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Портфель — оперативный срез</t>
+          <t>Средняя просрочка по департаментам</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
+          <t>оф. ТЗ ¶646; ТЗ 24</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>ФО-27</t>
+          <t>ФО-28</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Средняя просрочка по департаментам</t>
+          <t>Доля проблемных кредитов</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶646; ТЗ 24</t>
+          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
@@ -1817,17 +1817,17 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>ФО-28</t>
+          <t>ФО-47</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Доля проблемных кредитов</t>
+          <t>Реестр имущества на дату</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Портфель</t>
+          <t>Имущество</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
+          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
@@ -1854,17 +1854,17 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>ФО-47</t>
+          <t>ФО-53</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Реестр имущества на дату</t>
+          <t>Расчёт в валюте и курсовая разница за период</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Имущество</t>
+          <t>Расчёты</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
+          <t>оф. ТЗ ¶740</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>ФО-53</t>
+          <t>ФО-54</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Расчёт в валюте и курсовая разница за период</t>
+          <t>План-факт погашений</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Расчёты</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶740</t>
+          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
@@ -1920,7 +1920,11 @@
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr"/>
-      <c r="I43" s="7" t="inlineStr"/>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>Факт погашений против графика и плановых показателей</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -1928,17 +1932,17 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>ФО-54</t>
+          <t>ФО-55</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>План-факт погашений</t>
+          <t>Заявки по программам и статусам</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Заявка и комиссия</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
@@ -1948,7 +1952,7 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
+          <t>ТЗ 02; ТЗ 03</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
@@ -1957,11 +1961,7 @@
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr"/>
-      <c r="I44" s="7" t="inlineStr">
-        <is>
-          <t>Факт погашений против графика и плановых показателей</t>
-        </is>
-      </c>
+      <c r="I44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -1969,17 +1969,17 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>ФО-55</t>
+          <t>ФО-56</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Заявки по программам и статусам</t>
+          <t>План и факт выдачи</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Заявка и комиссия</t>
+          <t>Кредитная программа</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 02; ТЗ 03</t>
+          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
@@ -1998,7 +1998,11 @@
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr"/>
-      <c r="I45" s="7" t="inlineStr"/>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>Плановые показатели выдачи — справочник</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -2006,27 +2010,27 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>ФО-56</t>
+          <t>ФО-57</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>План и факт выдачи</t>
+          <t>Данные для расчёта ОКУ на дату</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Кредитная программа</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>служба рисков</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
+          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
@@ -2037,7 +2041,7 @@
       <c r="H46" s="7" t="inlineStr"/>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>Плановые показатели выдачи — справочник</t>
+          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
         </is>
       </c>
     </row>
@@ -2047,27 +2051,27 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>ФО-57</t>
+          <t>ФО-58</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Данные для расчёта ОКУ на дату</t>
+          <t>Изменения статусов кредитов за период</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>служба рисков</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
+          <t>оф. ТЗ ¶59</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
@@ -2076,11 +2080,7 @@
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr"/>
-      <c r="I47" s="7" t="inlineStr">
-        <is>
-          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
-        </is>
-      </c>
+      <c r="I47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -2088,27 +2088,27 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>ФО-58</t>
+          <t>ФО-59</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Изменения статусов кредитов за период</t>
+          <t>Кредитный риск портфеля</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>Правление</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶59</t>
+          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
@@ -2116,8 +2116,16 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="H48" s="7" t="inlineStr"/>
-      <c r="I48" s="7" t="inlineStr"/>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>Состав показателей — от службы рисков</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>Раз в квартал</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -2125,27 +2133,27 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>ФО-59</t>
+          <t>ФО-91</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Кредитный риск портфеля</t>
+          <t>Отчёт для Министерства финансов (заготовка)</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Внешняя отчётность</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Правление</t>
+          <t>Министерство финансов</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
+          <t>ТЗ 20 п. 13.7</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
@@ -2155,14 +2163,10 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Состав показателей — от службы рисков</t>
-        </is>
-      </c>
-      <c r="I49" s="7" t="inlineStr">
-        <is>
-          <t>Раз в квартал</t>
-        </is>
-      </c>
+          <t>Образец формы. Без образца к заморозке строка снимается</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -2170,12 +2174,12 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>ФО-91</t>
+          <t>ФО-92</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Министерства финансов (заготовка)</t>
+          <t>Отчёт для Кабинета Министров (заготовка)</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
@@ -2185,7 +2189,7 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Министерство финансов</t>
+          <t>Кабинет Министров</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -2211,12 +2215,12 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>ФО-92</t>
+          <t>ФО-93</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Кабинета Министров (заготовка)</t>
+          <t>Отчёт для Национального статистического комитета (заготовка)</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -2226,7 +2230,7 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Кабинет Министров</t>
+          <t>Нацстатком</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -2252,12 +2256,12 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>ФО-93</t>
+          <t>ФО-94</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Национального статистического комитета (заготовка)</t>
+          <t>Отчёт для банка-агента (заготовка)</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -2267,7 +2271,7 @@
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>Нацстатком</t>
+          <t>банк-агент</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -2293,80 +2297,39 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>ФО-94</t>
+          <t>ФО-95</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для банка-агента (заготовка)</t>
+          <t>Погашенные кредиты за период</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Внешняя отчётность</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>банк-агент</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 20 п. 13.7</t>
+          <t>решение владельца 29.10.2026: выделен из вида ФО-02; закрытие кредитно-залоговых дел и снятие обременений после погашения</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H53" s="11" t="inlineStr">
-        <is>
-          <t>Образец формы. Без образца к заморозке строка снимается</t>
-        </is>
-      </c>
+          <t>нет — новая форма</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr"/>
       <c r="I53" s="7" t="inlineStr"/>
     </row>
-    <row r="54">
-      <c r="A54" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>ФО-95</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>Погашенные кредиты за период</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Кредит</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>решение владельца 29.10.2026: выделен из вида ФО-02; закрытие кредитно-залоговых дел и снятие обременений после погашения</t>
-        </is>
-      </c>
-      <c r="G54" s="7" t="inlineStr">
-        <is>
-          <t>нет — новая форма</t>
-        </is>
-      </c>
-      <c r="H54" s="7" t="inlineStr"/>
-      <c r="I54" s="7" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A9:I54"/>
+  <autoFilter ref="A9:I53"/>
   <mergeCells count="5">
     <mergeCell ref="A7:I7"/>
     <mergeCell ref="A2:I2"/>

--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Перечень отчётов" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень отчётов'!$A$9:$I$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень отчётов'!$A$9:$I$52</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Перечень отчётов'!$9:$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -531,7 +531,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Отчётов: 36 (из них заготовок внешних форм: 4), видов отчётов: 8. Строк с ⚠: 5.</t>
+          <t>Отчётов: 35 (из них заготовок внешних форм: 4), видов отчётов: 8. Строк с ⚠: 5.</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Обозначения: оф. ТЗ ¶N — абзац официального технического задания; Порядок №41 — Порядок в редакции №41 от 06.07.2026; Положение №12 — о работе с залогом; Методика №15 — ожидаемые кредитные убытки (МСФО 9); Методика №16 — мониторинг целевого использования, утв. Правлением №20 от 19.12.2025; Методика №17 — прогнозные показатели погашения; Инструкция №14 — группы платёжеспособности заёмщиков; Политика №28 — управление рисками; Учётная политика №27; ПКМ №554 — о Фонде развития регионов, с Типовым положением; ТЗ NN — техническое задание модуля АСУБК; старая система — АСУБК предыдущего поставщика.</t>
+          <t>Обозначения: оф. ТЗ ¶N — абзац официального технического задания; Порядок №41 — Порядок в редакции №41 от 06.07.2026; Положение №12 — о работе с залогом; Методика №15 — ожидаемые кредитные убытки (МСФО 9); Методика №16 — мониторинг целевого использования, утв. Правлением №20 от 19.12.2025; Методика №17 — прогнозные показатели погашения; Инструкция №14 — группы платёжеспособности заёмщиков; Политика №28 — управление рисками; Учётная политика №27; ТЗ NN — техническое задание модуля АСУБК; старая система — АСУБК предыдущего поставщика.</t>
         </is>
       </c>
     </row>
@@ -1164,17 +1164,17 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>ФО-13</t>
+          <t>ФО-14</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование средств</t>
+          <t>Залоговое обеспечение — предметы</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1184,20 +1184,16 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶444–445, ¶869; Порядок №41 п. 6 пп. 3; Методика №16 пп. 4, 6, 7, 11; ПКМ №554 Типовое положение пп. 78, 80</t>
+          <t>оф. ТЗ ¶357, ¶361, ¶475, ¶511, ¶671–682; Порядок №41 п. 10; Положение №12 п. 4.1, прил. 2 п. 2.5; ТЗ 12; старая система</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Отчет по залогу»</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr"/>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>Бланки Методики №16 — ФО-75…ФО-78</t>
-        </is>
-      </c>
+      <c r="I24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -1205,12 +1201,12 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>ФО-14</t>
+          <t>ФО-15</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Залоговое обеспечение — предметы</t>
+          <t>Акты обследования залога</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -1225,16 +1221,20 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶357, ¶361, ¶475, ¶511, ¶671–682; Порядок №41 п. 10; Положение №12 п. 4.1, прил. 2 п. 2.5; ТЗ 12; старая система</t>
+          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Положение №12 п. 5.3; старая система</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по залогу»</t>
+          <t>старая система «Отчет по актам обследования»</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr"/>
-      <c r="I25" s="7" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик. Бланк акта — ФО-43</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>ФО-15</t>
+          <t>ФО-16</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Акты обследования залога</t>
+          <t>Снятие с ареста (запрета на отчуждение)</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -1262,20 +1262,16 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Положение №12 п. 5.3; старая система</t>
+          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по актам обследования»</t>
+          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr"/>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик. Бланк акта — ФО-43</t>
-        </is>
-      </c>
+      <c r="I26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -1283,17 +1279,17 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>ФО-16</t>
+          <t>ФО-17</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Снятие с ареста (запрета на отчуждение)</t>
+          <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -1303,57 +1299,57 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
+          <t>оф. ТЗ ¶93, ¶96, ¶557–593, ¶621–622; Порядок №41 пп. 20, 21, 25, 27–29, 37, 53, 58, 59, 61; ТЗ 13; старая система</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
+          <t>старая система «Отчет по взысканию»</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Отбор по виду документа взыскания, включая документы, которые система только учитывает (оф. ТЗ ¶557–585)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>ФО-17</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>Взыскание</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶93, ¶96, ¶557–593, ¶621–622; Порядок №41 пп. 20, 21, 25, 27–29, 37, 53, 58, 59, 61; ТЗ 13; старая система</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Отчет по взысканию»</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr"/>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>Отбор по виду документа взыскания, включая документы, которые система только учитывает (оф. ТЗ ¶557–585)</t>
-        </is>
-      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶582–583; старая система</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>старая система «Отчет ОИП»</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr"/>
+      <c r="I28" s="9" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="9" t="n">
@@ -1366,7 +1362,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
+          <t>вид «Претензии по областям за период»</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
@@ -1381,12 +1377,12 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶582–583; старая система</t>
+          <t>оф. ТЗ ¶553–556; образец практики</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>старая система «Отчет ОИП»</t>
+          <t>«Претензии по 7 областям.xls»</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr"/>
@@ -1403,7 +1399,7 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>вид «Претензии по областям за период»</t>
+          <t>вид «События фазы по датам и времени»</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
@@ -1418,53 +1414,57 @@
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶553–556; образец практики</t>
+          <t>оф. ТЗ ¶627</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>«Претензии по 7 областям.xls»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H30" s="9" t="inlineStr"/>
       <c r="I30" s="9" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="n">
+      <c r="A31" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>ФО-17</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>вид «События фазы по датам и времени»</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>Взыскание</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶627</t>
-        </is>
-      </c>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H31" s="9" t="inlineStr"/>
-      <c r="I31" s="9" t="inlineStr"/>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>ФО-18</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Оформление — комплектность кредитно-залогового дела</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Оформление</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>старая система «Отчет по оформлению»</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -1472,17 +1472,17 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>ФО-18</t>
+          <t>ФО-19</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Оформление — комплектность кредитно-залогового дела</t>
+          <t>Документооборот — входящие и исходящие</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Оформление</t>
+          <t>Документооборот</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -1492,12 +1492,12 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
+          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по оформлению»</t>
+          <t>старая система «Отчет по документообороту»</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr"/>
@@ -1513,17 +1513,17 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>ФО-19</t>
+          <t>ФО-20</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Документооборот — входящие и исходящие</t>
+          <t>Задания и их исполнение</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Документооборот</t>
+          <t>Задания</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -1533,12 +1533,12 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
+          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по документообороту»</t>
+          <t>старая система «Контроль исполнения» (частично)</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr"/>
@@ -1554,17 +1554,17 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>ФО-20</t>
+          <t>ФО-24</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Задания и их исполнение</t>
+          <t>Классификация — движение по группам платёжеспособности</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Задания</t>
+          <t>Классификация</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -1574,20 +1574,16 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
+          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>старая система «Контроль исполнения» (частично)</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик</t>
-        </is>
-      </c>
+      <c r="I34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -1595,17 +1591,17 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>ФО-24</t>
+          <t>ФО-25</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Классификация — движение по группам платёжеспособности</t>
+          <t>Кураторство — нагрузка и закрепление</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Классификация</t>
+          <t>Кураторство</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -1615,7 +1611,7 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
+          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
@@ -1627,78 +1623,78 @@
       <c r="I35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>ФО-25</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>Кураторство — нагрузка и закрепление</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>вид «Погашенные заёмщики: месяц × куратор»</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
         <is>
           <t>Кураторство</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H36" s="7" t="inlineStr"/>
-      <c r="I36" s="7" t="inlineStr"/>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>образцы практики</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>«Result_3.xlsx», «Result_6.xlsx»</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr"/>
+      <c r="I36" s="9" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="n">
+      <c r="A37" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>ФО-25</t>
-        </is>
-      </c>
-      <c r="C37" s="10" t="inlineStr">
-        <is>
-          <t>вид «Погашенные заёмщики: месяц × куратор»</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>Кураторство</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>образцы практики</t>
-        </is>
-      </c>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t>«Result_3.xlsx», «Result_6.xlsx»</t>
-        </is>
-      </c>
-      <c r="H37" s="9" t="inlineStr"/>
-      <c r="I37" s="9" t="inlineStr"/>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>ФО-26</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Портфель — оперативный срез</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Портфель</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr"/>
+      <c r="I37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -1706,12 +1702,12 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>ФО-26</t>
+          <t>ФО-27</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Портфель — оперативный срез</t>
+          <t>Средняя просрочка по департаментам</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
@@ -1726,7 +1722,7 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
+          <t>оф. ТЗ ¶646; ТЗ 24</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
@@ -1743,12 +1739,12 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>ФО-27</t>
+          <t>ФО-28</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Средняя просрочка по департаментам</t>
+          <t>Доля проблемных кредитов</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
@@ -1763,7 +1759,7 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶646; ТЗ 24</t>
+          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
@@ -1780,17 +1776,17 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>ФО-28</t>
+          <t>ФО-47</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Доля проблемных кредитов</t>
+          <t>Реестр имущества на дату</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Портфель</t>
+          <t>Имущество</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
@@ -1800,7 +1796,7 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
+          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
@@ -1817,17 +1813,17 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>ФО-47</t>
+          <t>ФО-53</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Реестр имущества на дату</t>
+          <t>Расчёт в валюте и курсовая разница за период</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Имущество</t>
+          <t>Расчёты</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
@@ -1837,7 +1833,7 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
+          <t>оф. ТЗ ¶740</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
@@ -1854,17 +1850,17 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>ФО-53</t>
+          <t>ФО-54</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Расчёт в валюте и курсовая разница за период</t>
+          <t>План-факт погашений</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Расчёты</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
@@ -1874,7 +1870,7 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶740</t>
+          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -1883,7 +1879,11 @@
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr"/>
-      <c r="I42" s="7" t="inlineStr"/>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>Факт погашений против графика и плановых показателей</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>ФО-54</t>
+          <t>ФО-55</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>План-факт погашений</t>
+          <t>Заявки по программам и статусам</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Заявка и комиссия</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
+          <t>ТЗ 02; ТЗ 03</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
@@ -1920,11 +1920,7 @@
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr"/>
-      <c r="I43" s="7" t="inlineStr">
-        <is>
-          <t>Факт погашений против графика и плановых показателей</t>
-        </is>
-      </c>
+      <c r="I43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -1932,17 +1928,17 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>ФО-55</t>
+          <t>ФО-56</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Заявки по программам и статусам</t>
+          <t>План и факт выдачи</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Заявка и комиссия</t>
+          <t>Кредитная программа</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
@@ -1952,7 +1948,7 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 02; ТЗ 03</t>
+          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
@@ -1961,7 +1957,11 @@
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr"/>
-      <c r="I44" s="7" t="inlineStr"/>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>Плановые показатели выдачи — справочник</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -1969,27 +1969,27 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>ФО-56</t>
+          <t>ФО-57</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>План и факт выдачи</t>
+          <t>Данные для расчёта ОКУ на дату</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Кредитная программа</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>служба рисков</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
+          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
@@ -2000,7 +2000,7 @@
       <c r="H45" s="7" t="inlineStr"/>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>Плановые показатели выдачи — справочник</t>
+          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
         </is>
       </c>
     </row>
@@ -2010,27 +2010,27 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>ФО-57</t>
+          <t>ФО-58</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Данные для расчёта ОКУ на дату</t>
+          <t>Изменения статусов кредитов за период</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>служба рисков</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
+          <t>оф. ТЗ ¶59</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
@@ -2039,11 +2039,7 @@
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr"/>
-      <c r="I46" s="7" t="inlineStr">
-        <is>
-          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
-        </is>
-      </c>
+      <c r="I46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -2051,27 +2047,27 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>ФО-58</t>
+          <t>ФО-59</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Изменения статусов кредитов за период</t>
+          <t>Кредитный риск портфеля</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>Правление</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶59</t>
+          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
@@ -2079,8 +2075,16 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr"/>
-      <c r="I47" s="7" t="inlineStr"/>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>Состав показателей — от службы рисков</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>Раз в квартал</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -2088,27 +2092,27 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>ФО-59</t>
+          <t>ФО-91</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Кредитный риск портфеля</t>
+          <t>Отчёт для Министерства финансов (заготовка)</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Внешняя отчётность</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Правление</t>
+          <t>Министерство финансов</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
+          <t>ТЗ 20 п. 13.7</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
@@ -2118,14 +2122,10 @@
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>Состав показателей — от службы рисков</t>
-        </is>
-      </c>
-      <c r="I48" s="7" t="inlineStr">
-        <is>
-          <t>Раз в квартал</t>
-        </is>
-      </c>
+          <t>Образец формы. Без образца к заморозке строка снимается</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>ФО-91</t>
+          <t>ФО-92</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Министерства финансов (заготовка)</t>
+          <t>Отчёт для Кабинета Министров (заготовка)</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Министерство финансов</t>
+          <t>Кабинет Министров</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>ФО-92</t>
+          <t>ФО-93</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Кабинета Министров (заготовка)</t>
+          <t>Отчёт для Национального статистического комитета (заготовка)</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Кабинет Министров</t>
+          <t>Нацстатком</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -2215,12 +2215,12 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>ФО-93</t>
+          <t>ФО-94</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Национального статистического комитета (заготовка)</t>
+          <t>Отчёт для банка-агента (заготовка)</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Нацстатком</t>
+          <t>банк-агент</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -2256,80 +2256,39 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>ФО-94</t>
+          <t>ФО-95</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для банка-агента (заготовка)</t>
+          <t>Погашенные кредиты за период</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Внешняя отчётность</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>банк-агент</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 20 п. 13.7</t>
+          <t>решение владельца 29.10.2026: выделен из вида ФО-02; закрытие кредитно-залоговых дел и снятие обременений после погашения</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H52" s="11" t="inlineStr">
-        <is>
-          <t>Образец формы. Без образца к заморозке строка снимается</t>
-        </is>
-      </c>
+          <t>нет — новая форма</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr"/>
       <c r="I52" s="7" t="inlineStr"/>
     </row>
-    <row r="53">
-      <c r="A53" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>ФО-95</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>Погашенные кредиты за период</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>Кредит</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>решение владельца 29.10.2026: выделен из вида ФО-02; закрытие кредитно-залоговых дел и снятие обременений после погашения</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>нет — новая форма</t>
-        </is>
-      </c>
-      <c r="H53" s="7" t="inlineStr"/>
-      <c r="I53" s="7" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A9:I53"/>
+  <autoFilter ref="A9:I52"/>
   <mergeCells count="5">
     <mergeCell ref="A7:I7"/>
     <mergeCell ref="A2:I2"/>

--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Перечень отчётов" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень отчётов'!$A$9:$I$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень отчётов'!$A$9:$I$53</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Перечень отчётов'!$9:$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -531,7 +531,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Отчётов: 35 (из них заготовок внешних форм: 4), видов отчётов: 8. Строк с ⚠: 5.</t>
+          <t>Отчётов: 35 (из них заготовок внешних форм: 4), видов отчётов: 9. Строк с ⚠: 5.</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Залоговое обеспечение — предметы</t>
+          <t>Предметы залога по состоянию на дату</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -1193,46 +1193,50 @@
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr"/>
-      <c r="I24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>Прежнее название — «Залоговое обеспечение — предметы»; в старой системе — «Отчет по залогу» («Информация по залогу»). Обеспеченность кредитов — вид отчёта</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>ФО-15</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>Акты обследования залога</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>ФО-14</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>вид «Обеспеченность кредитов залогом по состоянию на дату»</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>Залог</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Положение №12 п. 5.3; старая система</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Отчет по актам обследования»</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="inlineStr"/>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик. Бланк акта — ФО-43</t>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>Положение №12 прил. 1 пп. 2.3–2.4, прил. 2 п. 2.5; ТЗ 12</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr"/>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>Строка — кредит: сумма под риском, залоговая стоимость, порог, индекс обеспеченности, недостаёт залога. Справка по одному договору — бланк ФО-61</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1246,12 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>ФО-16</t>
+          <t>ФО-15</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Снятие с ареста (запрета на отчуждение)</t>
+          <t>Акты обследования залога</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -1262,16 +1266,20 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
+          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Положение №12 п. 5.3; старая система</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
+          <t>старая система «Отчет по актам обследования»</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr"/>
-      <c r="I26" s="7" t="inlineStr"/>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик. Бланк акта — ФО-43</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -1279,77 +1287,77 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
+          <t>ФО-16</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Снятие с ареста (запрета на отчуждение)</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Залог</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
           <t>ФО-17</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>Взыскание</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>оф. ТЗ ¶93, ¶96, ¶557–593, ¶621–622; Порядок №41 пп. 20, 21, 25, 27–29, 37, 53, 58, 59, 61; ТЗ 13; старая система</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>старая система «Отчет по взысканию»</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>Отбор по виду документа взыскания, включая документы, которые система только учитывает (оф. ТЗ ¶557–585)</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>ФО-17</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>Взыскание</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶582–583; старая система</t>
-        </is>
-      </c>
-      <c r="G28" s="9" t="inlineStr">
-        <is>
-          <t>старая система «Отчет ОИП»</t>
-        </is>
-      </c>
-      <c r="H28" s="9" t="inlineStr"/>
-      <c r="I28" s="9" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="9" t="n">
@@ -1362,7 +1370,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>вид «Претензии по областям за период»</t>
+          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
@@ -1377,12 +1385,12 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶553–556; образец практики</t>
+          <t>оф. ТЗ ¶582–583; старая система</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>«Претензии по 7 областям.xls»</t>
+          <t>старая система «Отчет ОИП»</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr"/>
@@ -1399,7 +1407,7 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>вид «События фазы по датам и времени»</t>
+          <t>вид «Претензии по областям за период»</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
@@ -1414,57 +1422,53 @@
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶627</t>
+          <t>оф. ТЗ ¶553–556; образец практики</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>«Претензии по 7 областям.xls»</t>
         </is>
       </c>
       <c r="H30" s="9" t="inlineStr"/>
       <c r="I30" s="9" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>ФО-18</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>Оформление — комплектность кредитно-залогового дела</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>Оформление</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Отчет по оформлению»</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr"/>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик</t>
-        </is>
-      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>ФО-17</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>вид «События фазы по датам и времени»</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>Взыскание</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶627</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr"/>
+      <c r="I31" s="9" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -1472,17 +1476,17 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>ФО-19</t>
+          <t>ФО-18</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Документооборот — входящие и исходящие</t>
+          <t>Оформление — комплектность кредитно-залогового дела</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Документооборот</t>
+          <t>Оформление</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -1492,12 +1496,12 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
+          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по документообороту»</t>
+          <t>старая система «Отчет по оформлению»</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr"/>
@@ -1513,17 +1517,17 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>ФО-20</t>
+          <t>ФО-19</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Задания и их исполнение</t>
+          <t>Документооборот — входящие и исходящие</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Задания</t>
+          <t>Документооборот</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -1533,12 +1537,12 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
+          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>старая система «Контроль исполнения» (частично)</t>
+          <t>старая система «Отчет по документообороту»</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr"/>
@@ -1554,17 +1558,17 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>ФО-24</t>
+          <t>ФО-20</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Классификация — движение по группам платёжеспособности</t>
+          <t>Задания и их исполнение</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Классификация</t>
+          <t>Задания</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -1574,16 +1578,20 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
+          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Контроль исполнения» (частично)</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" s="7" t="inlineStr"/>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -1591,17 +1599,17 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>ФО-25</t>
+          <t>ФО-24</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Кураторство — нагрузка и закрепление</t>
+          <t>Классификация — движение по группам платёжеспособности</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Кураторство</t>
+          <t>Классификация</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -1611,7 +1619,7 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
+          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
@@ -1623,78 +1631,78 @@
       <c r="I35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="n">
+      <c r="A36" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>ФО-25</t>
         </is>
       </c>
-      <c r="C36" s="10" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Кураторство — нагрузка и закрепление</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Кураторство</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr"/>
+      <c r="I36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>ФО-25</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>вид «Погашенные заёмщики: месяц × куратор»</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>Кураторство</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F36" s="9" t="inlineStr">
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
         <is>
           <t>образцы практики</t>
         </is>
       </c>
-      <c r="G36" s="9" t="inlineStr">
+      <c r="G37" s="9" t="inlineStr">
         <is>
           <t>«Result_3.xlsx», «Result_6.xlsx»</t>
         </is>
       </c>
-      <c r="H36" s="9" t="inlineStr"/>
-      <c r="I36" s="9" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>ФО-26</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Портфель — оперативный срез</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>Портфель</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr"/>
-      <c r="I37" s="7" t="inlineStr"/>
+      <c r="H37" s="9" t="inlineStr"/>
+      <c r="I37" s="9" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -1702,12 +1710,12 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>ФО-27</t>
+          <t>ФО-26</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Средняя просрочка по департаментам</t>
+          <t>Портфель — оперативный срез</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
@@ -1722,7 +1730,7 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶646; ТЗ 24</t>
+          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
@@ -1739,12 +1747,12 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>ФО-28</t>
+          <t>ФО-27</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Доля проблемных кредитов</t>
+          <t>Средняя просрочка по департаментам</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
@@ -1759,7 +1767,7 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
+          <t>оф. ТЗ ¶646; ТЗ 24</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
@@ -1776,17 +1784,17 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>ФО-47</t>
+          <t>ФО-28</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Реестр имущества на дату</t>
+          <t>Доля проблемных кредитов</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Имущество</t>
+          <t>Портфель</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
@@ -1796,7 +1804,7 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
+          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
@@ -1813,17 +1821,17 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>ФО-53</t>
+          <t>ФО-47</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Расчёт в валюте и курсовая разница за период</t>
+          <t>Реестр имущества на дату</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Расчёты</t>
+          <t>Имущество</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
@@ -1833,7 +1841,7 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶740</t>
+          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
@@ -1850,17 +1858,17 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>ФО-54</t>
+          <t>ФО-53</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>План-факт погашений</t>
+          <t>Расчёт в валюте и курсовая разница за период</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Расчёты</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
@@ -1870,7 +1878,7 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
+          <t>оф. ТЗ ¶740</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -1879,11 +1887,7 @@
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr"/>
-      <c r="I42" s="7" t="inlineStr">
-        <is>
-          <t>Факт погашений против графика и плановых показателей</t>
-        </is>
-      </c>
+      <c r="I42" s="7" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -1891,17 +1895,17 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>ФО-55</t>
+          <t>ФО-54</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Заявки по программам и статусам</t>
+          <t>План-факт погашений</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Заявка и комиссия</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
@@ -1911,7 +1915,7 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 02; ТЗ 03</t>
+          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
@@ -1920,7 +1924,11 @@
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr"/>
-      <c r="I43" s="7" t="inlineStr"/>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>Факт погашений против графика и плановых показателей</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -1928,17 +1936,17 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>ФО-56</t>
+          <t>ФО-55</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>План и факт выдачи</t>
+          <t>Заявки по программам и статусам</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Кредитная программа</t>
+          <t>Заявка и комиссия</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
@@ -1948,7 +1956,7 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
+          <t>ТЗ 02; ТЗ 03</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
@@ -1957,11 +1965,7 @@
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr"/>
-      <c r="I44" s="7" t="inlineStr">
-        <is>
-          <t>Плановые показатели выдачи — справочник</t>
-        </is>
-      </c>
+      <c r="I44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -1969,27 +1973,27 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>ФО-57</t>
+          <t>ФО-56</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Данные для расчёта ОКУ на дату</t>
+          <t>План и факт выдачи</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Кредитная программа</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>служба рисков</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
+          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
@@ -2000,7 +2004,7 @@
       <c r="H45" s="7" t="inlineStr"/>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
+          <t>Плановые показатели выдачи — справочник</t>
         </is>
       </c>
     </row>
@@ -2010,27 +2014,27 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>ФО-58</t>
+          <t>ФО-57</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Изменения статусов кредитов за период</t>
+          <t>Данные для расчёта ОКУ на дату</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>служба рисков</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶59</t>
+          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
@@ -2039,7 +2043,11 @@
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr"/>
-      <c r="I46" s="7" t="inlineStr"/>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -2047,27 +2055,27 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>ФО-59</t>
+          <t>ФО-58</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Кредитный риск портфеля</t>
+          <t>Изменения статусов кредитов за период</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>Правление</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
+          <t>оф. ТЗ ¶59</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
@@ -2075,16 +2083,8 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="H47" s="11" t="inlineStr">
-        <is>
-          <t>Состав показателей — от службы рисков</t>
-        </is>
-      </c>
-      <c r="I47" s="7" t="inlineStr">
-        <is>
-          <t>Раз в квартал</t>
-        </is>
-      </c>
+      <c r="H47" s="7" t="inlineStr"/>
+      <c r="I47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -2092,27 +2092,27 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>ФО-91</t>
+          <t>ФО-59</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Министерства финансов (заготовка)</t>
+          <t>Кредитный риск портфеля</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Внешняя отчётность</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Министерство финансов</t>
+          <t>Правление</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 20 п. 13.7</t>
+          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
@@ -2122,10 +2122,14 @@
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>Образец формы. Без образца к заморозке строка снимается</t>
-        </is>
-      </c>
-      <c r="I48" s="7" t="inlineStr"/>
+          <t>Состав показателей — от службы рисков</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>Раз в квартал</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -2133,12 +2137,12 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>ФО-92</t>
+          <t>ФО-91</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Кабинета Министров (заготовка)</t>
+          <t>Отчёт для Министерства финансов (заготовка)</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
@@ -2148,7 +2152,7 @@
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Кабинет Министров</t>
+          <t>Министерство финансов</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -2174,12 +2178,12 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>ФО-93</t>
+          <t>ФО-92</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Национального статистического комитета (заготовка)</t>
+          <t>Отчёт для Кабинета Министров (заготовка)</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
@@ -2189,7 +2193,7 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Нацстатком</t>
+          <t>Кабинет Министров</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -2215,12 +2219,12 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>ФО-94</t>
+          <t>ФО-93</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для банка-агента (заготовка)</t>
+          <t>Отчёт для Национального статистического комитета (заготовка)</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -2230,7 +2234,7 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>банк-агент</t>
+          <t>Нацстатком</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -2256,39 +2260,80 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
+          <t>ФО-94</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>Отчёт для банка-агента (заготовка)</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Внешняя отчётность</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>банк-агент</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>ТЗ 20 п. 13.7</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H52" s="11" t="inlineStr">
+        <is>
+          <t>Образец формы. Без образца к заморозке строка снимается</t>
+        </is>
+      </c>
+      <c r="I52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
           <t>ФО-95</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>Погашенные кредиты за период</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>Кредит</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F52" s="7" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
         <is>
           <t>решение владельца 29.10.2026: выделен из вида ФО-02; закрытие кредитно-залоговых дел и снятие обременений после погашения</t>
         </is>
       </c>
-      <c r="G52" s="7" t="inlineStr">
+      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>нет — новая форма</t>
         </is>
       </c>
-      <c r="H52" s="7" t="inlineStr"/>
-      <c r="I52" s="7" t="inlineStr"/>
+      <c r="H53" s="7" t="inlineStr"/>
+      <c r="I53" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A9:I52"/>
+  <autoFilter ref="A9:I53"/>
   <mergeCells count="5">
     <mergeCell ref="A7:I7"/>
     <mergeCell ref="A2:I2"/>

--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -886,7 +886,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Освоение и транши</t>
+          <t>Освоение кредитов по состоянию на дату</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -912,7 +912,7 @@
       <c r="H17" s="7" t="inlineStr"/>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>Данные для формы обеспечивает разработчик</t>
+          <t>Прежнее название — «Освоение и транши»; в старой системе отчёта не было, только разрез «Группа по освоению». Выдачи за период против плана — ФО-56</t>
         </is>
       </c>
     </row>

--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Перечень отчётов" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень отчётов'!$A$9:$I$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень отчётов'!$A$9:$I$54</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Перечень отчётов'!$9:$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -531,7 +531,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Отчётов: 35 (из них заготовок внешних форм: 4), видов отчётов: 9. Строк с ⚠: 5.</t>
+          <t>Отчётов: 35 (из них заготовок внешних форм: 4), видов отчётов: 10. Строк с ⚠: 5.</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Акты обследования залога</t>
+          <t>Акты обследования залога за период</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Положение №12 п. 5.3; старая система</t>
+          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Порядок №41 п. 10; Положение №12 п. 5.3, прил. 2 пп. 2.3–2.4; ТЗ 12; старая система</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
@@ -1277,46 +1277,50 @@
       <c r="H26" s="7" t="inlineStr"/>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>Данные для формы обеспечивает разработчик. Бланк акта — ФО-43</t>
+          <t>Прежнее название — «Акты обследования залога»; в старой системе — «Отчет по актам обследования» («Информация по актам обследования»). Бланк одного акта — ФО-43. Сроки обследования на дату — вид отчёта</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>ФО-16</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>Снятие с ареста (запрета на отчуждение)</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>ФО-15</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>вид «Сроки обследования предметов залога по состоянию на дату»</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>Залог</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="7" t="inlineStr"/>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>Положение №12 прил. 2 п. 2.3; Порядок №41 п. 10; ТЗ 12; старая система</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr"/>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>Строка — предмет в залоге: последнее обследование и исход, периодичность, следующее обследование, дней до него; просроченные — сверху. В старой системе — разрезы «Статус обследования» и «Состояние обследования» в «Отчете по залогу»</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -1324,77 +1328,77 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
+          <t>ФО-16</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Снятие с ареста (запрета на отчуждение)</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Залог</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
           <t>ФО-17</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>Взыскание</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>оф. ТЗ ¶93, ¶96, ¶557–593, ¶621–622; Порядок №41 пп. 20, 21, 25, 27–29, 37, 53, 58, 59, 61; ТЗ 13; старая система</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>старая система «Отчет по взысканию»</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr"/>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>Отбор по виду документа взыскания, включая документы, которые система только учитывает (оф. ТЗ ¶557–585)</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>ФО-17</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>Взыскание</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶582–583; старая система</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t>старая система «Отчет ОИП»</t>
-        </is>
-      </c>
-      <c r="H29" s="9" t="inlineStr"/>
-      <c r="I29" s="9" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="9" t="n">
@@ -1407,7 +1411,7 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>вид «Претензии по областям за период»</t>
+          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
@@ -1422,12 +1426,12 @@
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶553–556; образец практики</t>
+          <t>оф. ТЗ ¶582–583; старая система</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>«Претензии по 7 областям.xls»</t>
+          <t>старая система «Отчет ОИП»</t>
         </is>
       </c>
       <c r="H30" s="9" t="inlineStr"/>
@@ -1444,7 +1448,7 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>вид «События фазы по датам и времени»</t>
+          <t>вид «Претензии по областям за период»</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
@@ -1459,57 +1463,53 @@
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶627</t>
+          <t>оф. ТЗ ¶553–556; образец практики</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>«Претензии по 7 областям.xls»</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr"/>
       <c r="I31" s="9" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>ФО-18</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Оформление — комплектность кредитно-залогового дела</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Оформление</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Отчет по оформлению»</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr"/>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик</t>
-        </is>
-      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>ФО-17</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>вид «События фазы по датам и времени»</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>Взыскание</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶627</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr"/>
+      <c r="I32" s="9" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -1517,17 +1517,17 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>ФО-19</t>
+          <t>ФО-18</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Документооборот — входящие и исходящие</t>
+          <t>Оформление — комплектность кредитно-залогового дела</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Документооборот</t>
+          <t>Оформление</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -1537,12 +1537,12 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
+          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по документообороту»</t>
+          <t>старая система «Отчет по оформлению»</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr"/>
@@ -1558,17 +1558,17 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>ФО-20</t>
+          <t>ФО-19</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Задания и их исполнение</t>
+          <t>Документооборот — входящие и исходящие</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Задания</t>
+          <t>Документооборот</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
+          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>старая система «Контроль исполнения» (частично)</t>
+          <t>старая система «Отчет по документообороту»</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr"/>
@@ -1599,17 +1599,17 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>ФО-24</t>
+          <t>ФО-20</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Классификация — движение по группам платёжеспособности</t>
+          <t>Задания и их исполнение</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Классификация</t>
+          <t>Задания</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -1619,16 +1619,20 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
+          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Контроль исполнения» (частично)</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr"/>
-      <c r="I35" s="7" t="inlineStr"/>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -1636,17 +1640,17 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>ФО-25</t>
+          <t>ФО-24</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Кураторство — нагрузка и закрепление</t>
+          <t>Классификация — движение по группам платёжеспособности</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Кураторство</t>
+          <t>Классификация</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
@@ -1656,7 +1660,7 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
+          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
@@ -1668,78 +1672,78 @@
       <c r="I36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="n">
+      <c r="A37" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>ФО-25</t>
         </is>
       </c>
-      <c r="C37" s="10" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Кураторство — нагрузка и закрепление</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Кураторство</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr"/>
+      <c r="I37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>ФО-25</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>вид «Погашенные заёмщики: месяц × куратор»</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>Кураторство</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
         <is>
           <t>образцы практики</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr">
+      <c r="G38" s="9" t="inlineStr">
         <is>
           <t>«Result_3.xlsx», «Result_6.xlsx»</t>
         </is>
       </c>
-      <c r="H37" s="9" t="inlineStr"/>
-      <c r="I37" s="9" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>ФО-26</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>Портфель — оперативный срез</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Портфель</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H38" s="7" t="inlineStr"/>
-      <c r="I38" s="7" t="inlineStr"/>
+      <c r="H38" s="9" t="inlineStr"/>
+      <c r="I38" s="9" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -1747,12 +1751,12 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>ФО-27</t>
+          <t>ФО-26</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Средняя просрочка по департаментам</t>
+          <t>Портфель — оперативный срез</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
@@ -1767,7 +1771,7 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶646; ТЗ 24</t>
+          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
@@ -1784,12 +1788,12 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>ФО-28</t>
+          <t>ФО-27</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Доля проблемных кредитов</t>
+          <t>Средняя просрочка по департаментам</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
@@ -1804,7 +1808,7 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
+          <t>оф. ТЗ ¶646; ТЗ 24</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
@@ -1821,17 +1825,17 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>ФО-47</t>
+          <t>ФО-28</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Реестр имущества на дату</t>
+          <t>Доля проблемных кредитов</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Имущество</t>
+          <t>Портфель</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
@@ -1841,7 +1845,7 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
+          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
@@ -1858,17 +1862,17 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>ФО-53</t>
+          <t>ФО-47</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Расчёт в валюте и курсовая разница за период</t>
+          <t>Реестр имущества на дату</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Расчёты</t>
+          <t>Имущество</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
@@ -1878,7 +1882,7 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶740</t>
+          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -1895,17 +1899,17 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>ФО-54</t>
+          <t>ФО-53</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>План-факт погашений</t>
+          <t>Расчёт в валюте и курсовая разница за период</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Расчёты</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
@@ -1915,7 +1919,7 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
+          <t>оф. ТЗ ¶740</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
@@ -1924,11 +1928,7 @@
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr"/>
-      <c r="I43" s="7" t="inlineStr">
-        <is>
-          <t>Факт погашений против графика и плановых показателей</t>
-        </is>
-      </c>
+      <c r="I43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -1936,17 +1936,17 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>ФО-55</t>
+          <t>ФО-54</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Заявки по программам и статусам</t>
+          <t>План-факт погашений</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Заявка и комиссия</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 02; ТЗ 03</t>
+          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
@@ -1965,7 +1965,11 @@
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr"/>
-      <c r="I44" s="7" t="inlineStr"/>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>Факт погашений против графика и плановых показателей</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -1973,17 +1977,17 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>ФО-56</t>
+          <t>ФО-55</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>План и факт выдачи</t>
+          <t>Заявки по программам и статусам</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Кредитная программа</t>
+          <t>Заявка и комиссия</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
@@ -1993,7 +1997,7 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
+          <t>ТЗ 02; ТЗ 03</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
@@ -2002,11 +2006,7 @@
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr"/>
-      <c r="I45" s="7" t="inlineStr">
-        <is>
-          <t>Плановые показатели выдачи — справочник</t>
-        </is>
-      </c>
+      <c r="I45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -2014,27 +2014,27 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>ФО-57</t>
+          <t>ФО-56</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Данные для расчёта ОКУ на дату</t>
+          <t>План и факт выдачи</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Кредитная программа</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>служба рисков</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
+          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
@@ -2045,7 +2045,7 @@
       <c r="H46" s="7" t="inlineStr"/>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
+          <t>Плановые показатели выдачи — справочник</t>
         </is>
       </c>
     </row>
@@ -2055,27 +2055,27 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>ФО-58</t>
+          <t>ФО-57</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Изменения статусов кредитов за период</t>
+          <t>Данные для расчёта ОКУ на дату</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>служба рисков</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶59</t>
+          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
@@ -2084,7 +2084,11 @@
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr"/>
-      <c r="I47" s="7" t="inlineStr"/>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -2092,27 +2096,27 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>ФО-59</t>
+          <t>ФО-58</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Кредитный риск портфеля</t>
+          <t>Изменения статусов кредитов за период</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Правление</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
+          <t>оф. ТЗ ¶59</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
@@ -2120,16 +2124,8 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="H48" s="11" t="inlineStr">
-        <is>
-          <t>Состав показателей — от службы рисков</t>
-        </is>
-      </c>
-      <c r="I48" s="7" t="inlineStr">
-        <is>
-          <t>Раз в квартал</t>
-        </is>
-      </c>
+      <c r="H48" s="7" t="inlineStr"/>
+      <c r="I48" s="7" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -2137,27 +2133,27 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>ФО-91</t>
+          <t>ФО-59</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Министерства финансов (заготовка)</t>
+          <t>Кредитный риск портфеля</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Внешняя отчётность</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Министерство финансов</t>
+          <t>Правление</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 20 п. 13.7</t>
+          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
@@ -2167,10 +2163,14 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Образец формы. Без образца к заморозке строка снимается</t>
-        </is>
-      </c>
-      <c r="I49" s="7" t="inlineStr"/>
+          <t>Состав показателей — от службы рисков</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>Раз в квартал</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>ФО-92</t>
+          <t>ФО-91</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Кабинета Министров (заготовка)</t>
+          <t>Отчёт для Министерства финансов (заготовка)</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Кабинет Министров</t>
+          <t>Министерство финансов</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>ФО-93</t>
+          <t>ФО-92</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Национального статистического комитета (заготовка)</t>
+          <t>Отчёт для Кабинета Министров (заготовка)</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Нацстатком</t>
+          <t>Кабинет Министров</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>ФО-94</t>
+          <t>ФО-93</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для банка-агента (заготовка)</t>
+          <t>Отчёт для Национального статистического комитета (заготовка)</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>банк-агент</t>
+          <t>Нацстатком</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -2301,39 +2301,80 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
+          <t>ФО-94</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>Отчёт для банка-агента (заготовка)</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Внешняя отчётность</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>банк-агент</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>ТЗ 20 п. 13.7</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H53" s="11" t="inlineStr">
+        <is>
+          <t>Образец формы. Без образца к заморозке строка снимается</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
           <t>ФО-95</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>Погашенные кредиты за период</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>Кредит</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
         <is>
           <t>решение владельца 29.10.2026: выделен из вида ФО-02; закрытие кредитно-залоговых дел и снятие обременений после погашения</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr">
+      <c r="G54" s="7" t="inlineStr">
         <is>
           <t>нет — новая форма</t>
         </is>
       </c>
-      <c r="H53" s="7" t="inlineStr"/>
-      <c r="I53" s="7" t="inlineStr"/>
+      <c r="H54" s="7" t="inlineStr"/>
+      <c r="I54" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A9:I53"/>
+  <autoFilter ref="A9:I54"/>
   <mergeCells count="5">
     <mergeCell ref="A7:I7"/>
     <mergeCell ref="A2:I2"/>

--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Перечень отчётов" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень отчётов'!$A$9:$I$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень отчётов'!$A$9:$I$55</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Перечень отчётов'!$9:$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -531,7 +531,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Отчётов: 35 (из них заготовок внешних форм: 4), видов отчётов: 10. Строк с ⚠: 5.</t>
+          <t>Отчётов: 35 (из них заготовок внешних форм: 4), видов отчётов: 11. Строк с ⚠: 5.</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Снятие с ареста (запрета на отчуждение)</t>
+          <t>Снятие запрета на отчуждение за период</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
+          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Порядок №41 пп. 10, 64; Положение №12 п. 7.2, прил. 3; ТЗ 12; старая система</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
@@ -1357,85 +1357,93 @@
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr"/>
-      <c r="I28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>Прежнее название — «Снятие с ареста (запрета на отчуждение)»; в старой системе — «Отчет по снятию с ареста» («Информация по снятию с ареста»). Извещение о снятии — бланк ФО-90. Запреты, подлежащие снятию, на дату — вид отчёта</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>ФО-16</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>вид «Запреты, подлежащие снятию, по состоянию на дату»</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>Залог</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>Положение №12 п. 7.2, прил. 3; ТЗ 12</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr"/>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>Строка — предмет, на котором действует запрет, хотя обеспечиваемые кредиты закрыты или предмет выведен из договора: основание снятия, с какого дня запрет подлежит снятию, дней ожидания</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>ФО-17</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>Взыскание</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>оф. ТЗ ¶93, ¶96, ¶557–593, ¶621–622; Порядок №41 пп. 20, 21, 25, 27–29, 37, 53, 58, 59, 61; ТЗ 13; старая система</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>старая система «Отчет по взысканию»</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr"/>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr"/>
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>Отбор по виду документа взыскания, включая документы, которые система только учитывает (оф. ТЗ ¶557–585)</t>
         </is>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>ФО-17</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>Взыскание</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶582–583; старая система</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>старая система «Отчет ОИП»</t>
-        </is>
-      </c>
-      <c r="H30" s="9" t="inlineStr"/>
-      <c r="I30" s="9" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="9" t="n">
@@ -1448,7 +1456,7 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>вид «Претензии по областям за период»</t>
+          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
@@ -1463,12 +1471,12 @@
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶553–556; образец практики</t>
+          <t>оф. ТЗ ¶582–583; старая система</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>«Претензии по 7 областям.xls»</t>
+          <t>старая система «Отчет ОИП»</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr"/>
@@ -1485,7 +1493,7 @@
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>вид «События фазы по датам и времени»</t>
+          <t>вид «Претензии по областям за период»</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
@@ -1500,57 +1508,53 @@
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶627</t>
+          <t>оф. ТЗ ¶553–556; образец практики</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>«Претензии по 7 областям.xls»</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr"/>
       <c r="I32" s="9" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>ФО-18</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>Оформление — комплектность кредитно-залогового дела</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>Оформление</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Отчет по оформлению»</t>
-        </is>
-      </c>
-      <c r="H33" s="7" t="inlineStr"/>
-      <c r="I33" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик</t>
-        </is>
-      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>ФО-17</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>вид «События фазы по датам и времени»</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>Взыскание</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶627</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr"/>
+      <c r="I33" s="9" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -1558,17 +1562,17 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>ФО-19</t>
+          <t>ФО-18</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Документооборот — входящие и исходящие</t>
+          <t>Оформление — комплектность кредитно-залогового дела</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Документооборот</t>
+          <t>Оформление</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -1578,12 +1582,12 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
+          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по документообороту»</t>
+          <t>старая система «Отчет по оформлению»</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr"/>
@@ -1599,17 +1603,17 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>ФО-20</t>
+          <t>ФО-19</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Задания и их исполнение</t>
+          <t>Документооборот — входящие и исходящие</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Задания</t>
+          <t>Документооборот</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -1619,12 +1623,12 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
+          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>старая система «Контроль исполнения» (частично)</t>
+          <t>старая система «Отчет по документообороту»</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr"/>
@@ -1640,17 +1644,17 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>ФО-24</t>
+          <t>ФО-20</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Классификация — движение по группам платёжеспособности</t>
+          <t>Задания и их исполнение</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Классификация</t>
+          <t>Задания</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
@@ -1660,16 +1664,20 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
+          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Контроль исполнения» (частично)</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr"/>
-      <c r="I36" s="7" t="inlineStr"/>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -1677,17 +1685,17 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>ФО-25</t>
+          <t>ФО-24</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Кураторство — нагрузка и закрепление</t>
+          <t>Классификация — движение по группам платёжеспособности</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Кураторство</t>
+          <t>Классификация</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
@@ -1697,7 +1705,7 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
+          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
@@ -1709,78 +1717,78 @@
       <c r="I37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="n">
+      <c r="A38" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>ФО-25</t>
         </is>
       </c>
-      <c r="C38" s="10" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Кураторство — нагрузка и закрепление</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Кураторство</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr"/>
+      <c r="I38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>ФО-25</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>вид «Погашенные заёмщики: месяц × куратор»</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="D39" s="9" t="inlineStr">
         <is>
           <t>Кураторство</t>
         </is>
       </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
         <is>
           <t>образцы практики</t>
         </is>
       </c>
-      <c r="G38" s="9" t="inlineStr">
+      <c r="G39" s="9" t="inlineStr">
         <is>
           <t>«Result_3.xlsx», «Result_6.xlsx»</t>
         </is>
       </c>
-      <c r="H38" s="9" t="inlineStr"/>
-      <c r="I38" s="9" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>ФО-26</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>Портфель — оперативный срез</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>Портфель</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H39" s="7" t="inlineStr"/>
-      <c r="I39" s="7" t="inlineStr"/>
+      <c r="H39" s="9" t="inlineStr"/>
+      <c r="I39" s="9" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -1788,12 +1796,12 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>ФО-27</t>
+          <t>ФО-26</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Средняя просрочка по департаментам</t>
+          <t>Портфель — оперативный срез</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
@@ -1808,7 +1816,7 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶646; ТЗ 24</t>
+          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
@@ -1825,12 +1833,12 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>ФО-28</t>
+          <t>ФО-27</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Доля проблемных кредитов</t>
+          <t>Средняя просрочка по департаментам</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
@@ -1845,7 +1853,7 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
+          <t>оф. ТЗ ¶646; ТЗ 24</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
@@ -1862,17 +1870,17 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>ФО-47</t>
+          <t>ФО-28</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Реестр имущества на дату</t>
+          <t>Доля проблемных кредитов</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Имущество</t>
+          <t>Портфель</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
@@ -1882,7 +1890,7 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
+          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -1899,17 +1907,17 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>ФО-53</t>
+          <t>ФО-47</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Расчёт в валюте и курсовая разница за период</t>
+          <t>Реестр имущества на дату</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Расчёты</t>
+          <t>Имущество</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
@@ -1919,7 +1927,7 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶740</t>
+          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
@@ -1936,17 +1944,17 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>ФО-54</t>
+          <t>ФО-53</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>План-факт погашений</t>
+          <t>Расчёт в валюте и курсовая разница за период</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Расчёты</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
@@ -1956,7 +1964,7 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
+          <t>оф. ТЗ ¶740</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
@@ -1965,11 +1973,7 @@
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr"/>
-      <c r="I44" s="7" t="inlineStr">
-        <is>
-          <t>Факт погашений против графика и плановых показателей</t>
-        </is>
-      </c>
+      <c r="I44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -1977,17 +1981,17 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>ФО-55</t>
+          <t>ФО-54</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Заявки по программам и статусам</t>
+          <t>План-факт погашений</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Заявка и комиссия</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
@@ -1997,7 +2001,7 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 02; ТЗ 03</t>
+          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
@@ -2006,7 +2010,11 @@
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr"/>
-      <c r="I45" s="7" t="inlineStr"/>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>Факт погашений против графика и плановых показателей</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -2014,17 +2022,17 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>ФО-56</t>
+          <t>ФО-55</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>План и факт выдачи</t>
+          <t>Заявки по программам и статусам</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Кредитная программа</t>
+          <t>Заявка и комиссия</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
@@ -2034,7 +2042,7 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
+          <t>ТЗ 02; ТЗ 03</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
@@ -2043,11 +2051,7 @@
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr"/>
-      <c r="I46" s="7" t="inlineStr">
-        <is>
-          <t>Плановые показатели выдачи — справочник</t>
-        </is>
-      </c>
+      <c r="I46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -2055,27 +2059,27 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>ФО-57</t>
+          <t>ФО-56</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Данные для расчёта ОКУ на дату</t>
+          <t>План и факт выдачи</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Кредитная программа</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>служба рисков</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
+          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
@@ -2086,7 +2090,7 @@
       <c r="H47" s="7" t="inlineStr"/>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
+          <t>Плановые показатели выдачи — справочник</t>
         </is>
       </c>
     </row>
@@ -2096,27 +2100,27 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>ФО-58</t>
+          <t>ФО-57</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Изменения статусов кредитов за период</t>
+          <t>Данные для расчёта ОКУ на дату</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>служба рисков</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶59</t>
+          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
@@ -2125,7 +2129,11 @@
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr"/>
-      <c r="I48" s="7" t="inlineStr"/>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -2133,27 +2141,27 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>ФО-59</t>
+          <t>ФО-58</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Кредитный риск портфеля</t>
+          <t>Изменения статусов кредитов за период</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Правление</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
+          <t>оф. ТЗ ¶59</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
@@ -2161,16 +2169,8 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="H49" s="11" t="inlineStr">
-        <is>
-          <t>Состав показателей — от службы рисков</t>
-        </is>
-      </c>
-      <c r="I49" s="7" t="inlineStr">
-        <is>
-          <t>Раз в квартал</t>
-        </is>
-      </c>
+      <c r="H49" s="7" t="inlineStr"/>
+      <c r="I49" s="7" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -2178,27 +2178,27 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>ФО-91</t>
+          <t>ФО-59</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Министерства финансов (заготовка)</t>
+          <t>Кредитный риск портфеля</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Внешняя отчётность</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Министерство финансов</t>
+          <t>Правление</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 20 п. 13.7</t>
+          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
@@ -2208,10 +2208,14 @@
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>Образец формы. Без образца к заморозке строка снимается</t>
-        </is>
-      </c>
-      <c r="I50" s="7" t="inlineStr"/>
+          <t>Состав показателей — от службы рисков</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>Раз в квартал</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -2219,12 +2223,12 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>ФО-92</t>
+          <t>ФО-91</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Кабинета Министров (заготовка)</t>
+          <t>Отчёт для Министерства финансов (заготовка)</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -2234,7 +2238,7 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Кабинет Министров</t>
+          <t>Министерство финансов</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -2260,12 +2264,12 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>ФО-93</t>
+          <t>ФО-92</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Национального статистического комитета (заготовка)</t>
+          <t>Отчёт для Кабинета Министров (заготовка)</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -2275,7 +2279,7 @@
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>Нацстатком</t>
+          <t>Кабинет Министров</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -2301,12 +2305,12 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>ФО-94</t>
+          <t>ФО-93</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для банка-агента (заготовка)</t>
+          <t>Отчёт для Национального статистического комитета (заготовка)</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -2316,7 +2320,7 @@
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>банк-агент</t>
+          <t>Нацстатком</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
@@ -2342,39 +2346,80 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
+          <t>ФО-94</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>Отчёт для банка-агента (заготовка)</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Внешняя отчётность</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>банк-агент</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>ТЗ 20 п. 13.7</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H54" s="11" t="inlineStr">
+        <is>
+          <t>Образец формы. Без образца к заморозке строка снимается</t>
+        </is>
+      </c>
+      <c r="I54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
           <t>ФО-95</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>Погашенные кредиты за период</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>Кредит</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
         <is>
           <t>решение владельца 29.10.2026: выделен из вида ФО-02; закрытие кредитно-залоговых дел и снятие обременений после погашения</t>
         </is>
       </c>
-      <c r="G54" s="7" t="inlineStr">
+      <c r="G55" s="7" t="inlineStr">
         <is>
           <t>нет — новая форма</t>
         </is>
       </c>
-      <c r="H54" s="7" t="inlineStr"/>
-      <c r="I54" s="7" t="inlineStr"/>
+      <c r="H55" s="7" t="inlineStr"/>
+      <c r="I55" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A9:I54"/>
+  <autoFilter ref="A9:I55"/>
   <mergeCells count="5">
     <mergeCell ref="A7:I7"/>
     <mergeCell ref="A2:I2"/>

--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -1415,7 +1415,7 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
+          <t>Меры взыскания за период</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶93, ¶96, ¶557–593, ¶621–622; Порядок №41 пп. 20, 21, 25, 27–29, 37, 53, 58, 59, 61; ТЗ 13; старая система</t>
+          <t>оф. ТЗ ¶93, ¶96, ¶553–593, ¶621–622; Порядок №41 пп. 16, 20, 21, 25, 27–29, 37, 53, 58, 59, 61; ТЗ 13; старая система</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
@@ -1441,7 +1441,7 @@
       <c r="H30" s="7" t="inlineStr"/>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>Отбор по виду документа взыскания, включая документы, которые система только учитывает (оф. ТЗ ¶557–585)</t>
+          <t>Прежнее название — «Взыскание — реестр принятых мер (процедуры, фазы, события)»; в старой системе — «Отчет по взысканию». Строка — мера журнала взыскания под строкой требования (кредит × обязанное лицо); отбор по виду меры, включая документы, которые система только учитывает (оф. ТЗ ¶557–585)</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
+          <t>вид «Исполнительные листы на исполнении за период»</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
@@ -1471,16 +1471,20 @@
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶582–583; старая система</t>
+          <t>оф. ТЗ ¶579–585; Порядок №41 пп. 27–29, 37; ТЗ 13; старая система</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>старая система «Отчет ОИП»</t>
+          <t>старая система «Отчет ОИП», «Отчет ОИП копия»</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr"/>
-      <c r="I31" s="9" t="inlineStr"/>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>Прежнее название — «ОИП — исполнительные листы в органе исполнительного производства». Строка — лист: присуждено, взыскано за период и всего, остаток</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="n">
@@ -1493,7 +1497,7 @@
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>вид «Претензии по областям за период»</t>
+          <t>вид «Претензии за период»</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
@@ -1508,7 +1512,7 @@
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶553–556; образец практики</t>
+          <t>оф. ТЗ ¶553–556; Порядок №41 пп. 16, 20; ТЗ 13; образец практики</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
@@ -1517,7 +1521,11 @@
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr"/>
-      <c r="I32" s="9" t="inlineStr"/>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>Прежнее название — «Претензии по областям за период». Строка — претензия: направлено, вручено, срок, исход</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="n">
@@ -1530,7 +1538,7 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>вид «События фазы по датам и времени»</t>
+          <t>вид «Судебные заседания за период»</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
@@ -1545,7 +1553,7 @@
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶627</t>
+          <t>оф. ТЗ ¶589–593, ¶627; ТЗ 13</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
@@ -1554,7 +1562,11 @@
         </is>
       </c>
       <c r="H33" s="9" t="inlineStr"/>
-      <c r="I33" s="9" t="inlineStr"/>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>Прежнее название — «События фазы по датам и времени». Строка — заседание суда с датой и временем</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">

--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -1579,12 +1579,12 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Оформление — комплектность кредитно-залогового дела</t>
+          <t>Комплектность кредитно-залоговых дел по состоянию на дату</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Оформление</t>
+          <t>Заёмщик</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
+          <t>оф. ТЗ ¶346–347; Порядок №41 пп. 13–14, п. 19 пп. 2; ТЗ 04; ТЗ 05 §13; ТЗ 12 §13; старая система</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
@@ -1605,7 +1605,7 @@
       <c r="H34" s="7" t="inlineStr"/>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>Данные для формы обеспечивает разработчик</t>
+          <t>Прежнее название — «Оформление — комплектность кредитно-залогового дела»; в старой системе — «Отчет по оформлению» («Информация по оформлению документации»). Строка — обязательный документ досье заёмщика под строкой объекта (документы заёмщика, кредит, предмет залога); комплект объявляют модули-владельцы, отчёт считает так же, как вкладки «Документы» карточек; по умолчанию — только неполные дела</t>
         </is>
       </c>
     </row>

--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Документооборот — входящие и исходящие</t>
+          <t>Документы и их исполнение за период</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
+          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23 §4.3, §9, §13.4; старая система</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
@@ -1646,7 +1646,7 @@
       <c r="H35" s="7" t="inlineStr"/>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>Данные для формы обеспечивает разработчик</t>
+          <t>Прежнее название — «Документооборот — входящие и исходящие»; в старой системе — «Отчет по документообороту» («Информация по документообороту»). Строка — зарегистрированный документ под видом и типом: исполнитель, контролёр, срок, дата исполнения; счётчики — расчётные показатели по документообороту (зарегистрировано, в работе, срок истёк, исполнено в срок и с опозданием, отказано, аннулировано, процент исполнения) от объекта статистики «документ»; журнал регистрации одного вида — ФО-66</t>
         </is>
       </c>
     </row>

--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -1661,7 +1661,7 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Задания и их исполнение</t>
+          <t>Задания и их исполнение за период</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
+          <t>оф. ТЗ ¶707–716, ¶1022–1033; старая система</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
@@ -1687,7 +1687,7 @@
       <c r="H36" s="7" t="inlineStr"/>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>Данные для формы обеспечивает разработчик</t>
+          <t>Прежнее название — «Задания и их исполнение»; в старой системе — «Контроль исполнения» (список задач по документам, поставленных пользователем). Строка — задание под подразделением исполнителя, исполнителем и источником задания: действие, объект, контролёр, срок, дата закрытия, состояние, сумма по заданию; счётчики — расчётные показатели по заданиям (назначено, в работе, срок истёк, исполнено в срок и с опозданием, отказано, снято, отпало, сумма по заданиям, процент исполнения) от объекта статистики «Задание»; документы — ФО-19, своя очередь сотрудника — экран «Мои задания»</t>
         </is>
       </c>
     </row>

--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -1702,7 +1702,7 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Классификация — движение по группам платёжеспособности</t>
+          <t>Движение по группам платёжеспособности за период</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
+          <t>оф. ТЗ ¶743–752; Порядок №41 пп. 3, 14, 21, 29, 58, 59, 61, 63–65; Инструкция №14 пп. 5–6; ТЗ 17</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
@@ -1726,7 +1726,11 @@
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr"/>
-      <c r="I37" s="7" t="inlineStr"/>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Прежнее название — «Классификация — движение по группам платёжеспособности»; в старой системе такого отчёта не было (группа и подгруппа заёмщика ставились вручную и были только разрезами). Строка — заёмщик под группой на начало периода и переходом в группу на конец: куратор, дата перехода, число переходов, остаток основного долга на начало и на конец, основание из объяснения классификатора; первый уровень — состав групп на начало; группу ставит классификатор, отчёт её читает</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">

--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Кураторство — нагрузка и закрепление</t>
+          <t>Нагрузка кураторов по состоянию на дату</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
@@ -1767,7 +1767,11 @@
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr"/>
-      <c r="I38" s="7" t="inlineStr"/>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>Прежнее название — «Кураторство — нагрузка и закрепление»; в старой системе такого отчёта не было — куратор был только разрезом отчётов по кредитам. Строка — закрепление объекта (заявка, кредит, предмет залога, требование по взысканию, предложение и объект имущества) за куратором на дату под департаментом, куратором и заёмщиком: с какого дня и каким источником закреплено (правило, рука, фолбэк); счётчики объектов в работе по ролям, остаток основного долга и просроченная задолженность — у кредитов; кредиты по куратору — также ФО-02 и ФО-01 разрезом «Куратор»</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="n">

--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -1858,12 +1858,12 @@
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Средняя просрочка по департаментам</t>
+          <t>Эпизоды просрочки за период</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Портфель</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶646; ТЗ 24</t>
+          <t>оф. ТЗ ¶646, ¶659; Порядок №41 п. 6 пп. 1, 6, 7, п. 16; ТЗ 18 §9.5; ТЗ 19 §3.1; ТЗ 24</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
@@ -1882,7 +1882,11 @@
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr"/>
-      <c r="I41" s="7" t="inlineStr"/>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>Прежнее название — «Средняя просрочка по департаментам» (средние дни просрочки по подразделениям на дату); в старой системе такого отчёта не было. Строка — эпизод просрочки (кредит × слой долга × начало) под департаментом, куратором, заёмщиком и кредитом: слой, закрытие и чем закрыт, длительность; счётчики «тянулись на начало · начались · вылечены · закрыты иначе · тянутся на конец», просрочено на конец периода, средняя длительность вылеченных и тянущихся; суммы и дни просрочки на дату — ФО-01</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">

--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -1899,12 +1899,12 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Доля проблемных кредитов</t>
+          <t>Доля проблемных кредитов по состоянию на дату</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Портфель</t>
+          <t>Классификация</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
+          <t>Порядок №41 п. 6 пп. 7, пп. 14–65; Инструкция №14; ТЗ 17; ТЗ 24 п. 4.13</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -1923,7 +1923,11 @@
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr"/>
-      <c r="I42" s="7" t="inlineStr"/>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>В старой системе такого отчёта не было: группа заёмщика была только разрезом. Строка — кредит под департаментом, куратором и заёмщиком: группа платёжеспособности на дату, заёмщики и кредиты всего и проблемных, остаток основного долга всего и проблемных с разбивкой по группам 1.2 · 2.1–2.3 · 3.1–3.2 · 4, доля проблемных в строках разрезов; проблемный — группа заёмщика на дату не 1.1 (принято в системе); квартальная доля для Правления — ФО-59</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">

--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Перечень отчётов" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень отчётов'!$A$9:$I$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень отчётов'!$A$9:$I$56</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Перечень отчётов'!$9:$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -531,7 +531,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Отчётов: 35 (из них заготовок внешних форм: 4), видов отчётов: 11. Строк с ⚠: 5.</t>
+          <t>Отчётов: 35 (из них заготовок внешних форм: 4), видов отчётов: 12. Строк с ⚠: 5.</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Реестр имущества на дату</t>
+          <t>Объекты имущества по состоянию на дату</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
+          <t>оф. ТЗ ¶531–537; Порядок №41 пп. 33–35, 49; Инструкция о принятии имущества пп. 5, 24–27, 34–35, 42–49, 57–63; ТЗ 22</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
@@ -1964,44 +1964,52 @@
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr"/>
-      <c r="I43" s="7" t="inlineStr"/>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>Прежнее название — «Реестр имущества на дату»; в старой системе имущества не было — принятие проходило только платежом вида «принятие имущества в счёт погашения». Строка — объект имущества Фонда под состоянием на дату и видом имущества: количество, источник, обязанное лицо, переход права, куратор имущества, обременение, состояние доплаты; учётная стоимость, расходы, договор купли-продажи (цена, оплачено, остаток, просрочено), доплата отчуждателю (сумма, выплачено), дней на учёте и просрочки оплаты. Предложения имущества — вид отчёта</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="n">
+      <c r="A44" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>ФО-53</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>Расчёт в валюте и курсовая разница за период</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Расчёты</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶740</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H44" s="7" t="inlineStr"/>
-      <c r="I44" s="7" t="inlineStr"/>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>ФО-47</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>вид «Предложения имущества за период»</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>Имущество</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶531–532; Порядок №41 п. 35; Инструкция о принятии имущества пп. 6–19; ТЗ 22</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H44" s="9" t="inlineStr"/>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>Строка — позиция предложения под источником и предложением: срок ответа и дата ответа, решение органа, итог позиции (принята, отказана, отозвана, принятие не состоялось, в работе), объект из принятой позиции, стоимость предложенного и принятого, дней рассмотрения. Отказ Фонда и отзыв источником — раздельно</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -2009,17 +2017,17 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>ФО-54</t>
+          <t>ФО-53</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>План-факт погашений</t>
+          <t>Расчёт в валюте и курсовая разница за период</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Расчёты</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
@@ -2029,7 +2037,7 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
+          <t>оф. ТЗ ¶740</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
@@ -2038,11 +2046,7 @@
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr"/>
-      <c r="I45" s="7" t="inlineStr">
-        <is>
-          <t>Факт погашений против графика и плановых показателей</t>
-        </is>
-      </c>
+      <c r="I45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -2050,17 +2054,17 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>ФО-55</t>
+          <t>ФО-54</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Заявки по программам и статусам</t>
+          <t>План-факт погашений</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Заявка и комиссия</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
@@ -2070,7 +2074,7 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 02; ТЗ 03</t>
+          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
@@ -2079,7 +2083,11 @@
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr"/>
-      <c r="I46" s="7" t="inlineStr"/>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>Факт погашений против графика и плановых показателей</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -2087,17 +2095,17 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>ФО-56</t>
+          <t>ФО-55</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>План и факт выдачи</t>
+          <t>Заявки по программам и статусам</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Кредитная программа</t>
+          <t>Заявка и комиссия</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
@@ -2107,7 +2115,7 @@
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
+          <t>ТЗ 02; ТЗ 03</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
@@ -2116,11 +2124,7 @@
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr"/>
-      <c r="I47" s="7" t="inlineStr">
-        <is>
-          <t>Плановые показатели выдачи — справочник</t>
-        </is>
-      </c>
+      <c r="I47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -2128,27 +2132,27 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>ФО-57</t>
+          <t>ФО-56</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Данные для расчёта ОКУ на дату</t>
+          <t>План и факт выдачи</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Кредитная программа</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>служба рисков</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
+          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
@@ -2159,7 +2163,7 @@
       <c r="H48" s="7" t="inlineStr"/>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
+          <t>Плановые показатели выдачи — справочник</t>
         </is>
       </c>
     </row>
@@ -2169,27 +2173,27 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>ФО-58</t>
+          <t>ФО-57</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Изменения статусов кредитов за период</t>
+          <t>Данные для расчёта ОКУ на дату</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>служба рисков</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶59</t>
+          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
@@ -2198,7 +2202,11 @@
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr"/>
-      <c r="I49" s="7" t="inlineStr"/>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -2206,27 +2214,27 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>ФО-59</t>
+          <t>ФО-58</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Кредитный риск портфеля</t>
+          <t>Изменения статусов кредитов за период</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Правление</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
+          <t>оф. ТЗ ¶59</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
@@ -2234,16 +2242,8 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="H50" s="11" t="inlineStr">
-        <is>
-          <t>Состав показателей — от службы рисков</t>
-        </is>
-      </c>
-      <c r="I50" s="7" t="inlineStr">
-        <is>
-          <t>Раз в квартал</t>
-        </is>
-      </c>
+      <c r="H50" s="7" t="inlineStr"/>
+      <c r="I50" s="7" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -2251,27 +2251,27 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>ФО-91</t>
+          <t>ФО-59</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Министерства финансов (заготовка)</t>
+          <t>Кредитный риск портфеля</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Внешняя отчётность</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Министерство финансов</t>
+          <t>Правление</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 20 п. 13.7</t>
+          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
@@ -2281,10 +2281,14 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Образец формы. Без образца к заморозке строка снимается</t>
-        </is>
-      </c>
-      <c r="I51" s="7" t="inlineStr"/>
+          <t>Состав показателей — от службы рисков</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>Раз в квартал</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -2292,12 +2296,12 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>ФО-92</t>
+          <t>ФО-91</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Кабинета Министров (заготовка)</t>
+          <t>Отчёт для Министерства финансов (заготовка)</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -2307,7 +2311,7 @@
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>Кабинет Министров</t>
+          <t>Министерство финансов</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -2333,12 +2337,12 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>ФО-93</t>
+          <t>ФО-92</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Национального статистического комитета (заготовка)</t>
+          <t>Отчёт для Кабинета Министров (заготовка)</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -2348,7 +2352,7 @@
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>Нацстатком</t>
+          <t>Кабинет Министров</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
@@ -2374,12 +2378,12 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>ФО-94</t>
+          <t>ФО-93</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для банка-агента (заготовка)</t>
+          <t>Отчёт для Национального статистического комитета (заготовка)</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
@@ -2389,7 +2393,7 @@
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>банк-агент</t>
+          <t>Нацстатком</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
@@ -2415,39 +2419,80 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
+          <t>ФО-94</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>Отчёт для банка-агента (заготовка)</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Внешняя отчётность</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>банк-агент</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>ТЗ 20 п. 13.7</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H55" s="11" t="inlineStr">
+        <is>
+          <t>Образец формы. Без образца к заморозке строка снимается</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="n">
+        <v>47</v>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
           <t>ФО-95</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>Погашенные кредиты за период</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>Кредит</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
         <is>
           <t>решение владельца 29.10.2026: выделен из вида ФО-02; закрытие кредитно-залоговых дел и снятие обременений после погашения</t>
         </is>
       </c>
-      <c r="G55" s="7" t="inlineStr">
+      <c r="G56" s="7" t="inlineStr">
         <is>
           <t>нет — новая форма</t>
         </is>
       </c>
-      <c r="H55" s="7" t="inlineStr"/>
-      <c r="I55" s="7" t="inlineStr"/>
+      <c r="H56" s="7" t="inlineStr"/>
+      <c r="I56" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A9:I55"/>
+  <autoFilter ref="A9:I56"/>
   <mergeCells count="5">
     <mergeCell ref="A7:I7"/>
     <mergeCell ref="A2:I2"/>

--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -2022,7 +2022,7 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Расчёт в валюте и курсовая разница за период</t>
+          <t>Курсовая разница по основному долгу за период</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶740</t>
+          <t>оф. ТЗ ¶740; ТЗ 18; старая система</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
@@ -2046,7 +2046,11 @@
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr"/>
-      <c r="I45" s="7" t="inlineStr"/>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>Прежнее название — «Расчёт в валюте и курсовая разница за период»; в старой системе отдельного отчёта не было — колонка «Курсовая разница» у кредита в отчёте по задолженности. Строка — кредит в иностранной валюте под валютой и заёмщиком: основной долг на начало, выдано, погашено, списано, курсовая разница и на конец — в сомах, под кредитом и под валютой — то же в валюте договора. Курсовая разница по процентам и штрафам — в ФО-07</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">

--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>План-факт погашений</t>
+          <t>План-факт погашений за период</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
+          <t>оф. ТЗ ¶75, ¶489, ¶660–663; ТЗ 05 (план кредита)</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
@@ -2089,7 +2089,7 @@
       <c r="H46" s="7" t="inlineStr"/>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>Факт погашений против графика и плановых показателей</t>
+          <t>Факт погашений против записанного плана и графика; в старой системе не было. Строка — кредит под департаментом, куратором и заёмщиком: по графику (как ФО-05), по плану (как ФО-06), погашено (как ФО-04), недобор к плану, исполнение плана и погашено к графику, %; месяц без плана в исполнение не входит, его погашение — справочно</t>
         </is>
       </c>
     </row>

--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -2104,7 +2104,7 @@
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Заявки по программам и статусам</t>
+          <t>Заявки на кредит за период</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 02; ТЗ 03</t>
+          <t>ТЗ 02; ТЗ 03; ТЗ 20 п. 13.14</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
@@ -2128,7 +2128,11 @@
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr"/>
-      <c r="I47" s="7" t="inlineStr"/>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>Прежнее название — «Заявки по программам и статусам»; в старой системе отчёта по заявкам не было. Строка — заявка под кредитной программой, статусом и заёмщиком: кредитный специалист, стадия, запрошено, одобрено комиссией, доля одобренного по заявкам с решением, дни в рассмотрении, протокол и кредитный договор; заявки в нагрузке специалистов — ФО-25</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">

--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -2145,12 +2145,12 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>План и факт выдачи</t>
+          <t>План-факт освоения кредитов за период</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Кредитная программа</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
+          <t>оф. ТЗ ¶648–649; ТЗ 05 §8; ТЗ 20 п. 5.32–5.34, 13.15</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
@@ -2171,7 +2171,7 @@
       <c r="H48" s="7" t="inlineStr"/>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>Плановые показатели выдачи — справочник</t>
+          <t>Прежнее название — «План и факт выдачи» (общий стартовый отчёт ТЗ 20 п. 13.15); в старой системе не было. Строка — кредит под департаментом, куратором и заёмщиком: освоено за период против годового плана департамента из справочника «Плановые показатели» (показатель «План выдачи»), осталось освоить до плана, выполнение плана, %; департамент с планом — строкой и без освоений; незавершённое освоение на дату — ФО-08</t>
         </is>
       </c>
     </row>

--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -2186,7 +2186,7 @@
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Данные для расчёта ОКУ на дату</t>
+          <t>Данные для расчёта ОКУ по состоянию на дату</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
+          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27; ТЗ 19 §15</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
@@ -2212,7 +2212,7 @@
       <c r="H49" s="7" t="inlineStr"/>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
+          <t>Ожидаемые кредитные убытки (ОКУ) по МСФО 9 — входные данные службе рисков на отчётную дату. Строка — кредит под группой платёжеспособности и заёмщиком: задолженность всего (основной долг, проценты, штрафы), просроченная, не освоено по договору, ставка, срок возврата, группа и категория риска, дата реструктуризации, оценочная стоимость залога и дата оценки, дни просрочки; входит и кредит без освоения (обязательство по выдаче). Сам расчёт ОКУ — стадии, вероятность дефолта, уровень потерь, резерв — у службы рисков, вне системы</t>
         </is>
       </c>
     </row>

--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -2242,7 +2242,7 @@
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶59</t>
+          <t>оф. ТЗ ¶59; ТЗ 05 §6</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
@@ -2251,7 +2251,11 @@
         </is>
       </c>
       <c r="H50" s="7" t="inlineStr"/>
-      <c r="I50" s="7" t="inlineStr"/>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>Новая форма: в старой системе отчёта не было (статус кредита — ручной справочник «Действует · Нулевая сверка · Отменён · Оформление» без истории). Строка — изменение статуса (регистрация, вступление в действие, закрытие: погашен, списан, расторгнут) или перевод долга под кредитом и заёмщиком: дата, было → стало, основание, когда и кем внесено, счётчики по видам; реструктуризация — не статус (ФО-09, вид «Изменения условий»)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">

--- a/docs/perechen-otchetov/Перечень-отчётов.xlsx
+++ b/docs/perechen-otchetov/Перечень-отчётов.xlsx
@@ -2268,7 +2268,7 @@
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>Кредитный риск портфеля</t>
+          <t>Кредитный риск портфеля за период</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
+          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10; Порядок №41 пп. 11, 14–65; ТЗ 19 §15</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>Раз в квартал</t>
+          <t>Новая форма: в старой системе отчёта не было (Политика №28 п. 5.4.4 — отчёт отдела риск-менеджмента Правлению не реже раза в квартал). Строка — показатель портфеля на начало и конец периода (по умолчанию — квартал) с изменением, в шести разделах: портфель и движение остатка, просроченная задолженность (кредиты, сумма, остаток кредитов с просрочкой до и более 180 дней, доля, средняя длительность), группы платёжеспособности и доля проблемных, концентрация (крупнейший заёмщик, пятёрка крупнейших), обеспеченность залогом, реструктуризация; каждый показатель — по правилу своего отчёта (ФО-01, 08, 10, 14, 24, 27, 28, 57). Резерв и ожидаемые кредитные убытки — у службы рисков вне системы (входные данные — ФО-57)</t>
         </is>
       </c>
     </row>
